--- a/uni_skills_refined.xlsx
+++ b/uni_skills_refined.xlsx
@@ -731,7 +731,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Academic Honesty Understanding</t>
+          <t>Source Acknowledgement</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>academic integrity; academic honesty; plagiarism prevention; research ethics; referencing styles</t>
+          <t>academic integrity; citation management; source; acknowledgement; referencing styles</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -780,16 +780,16 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t>MIS re-refinement: Structure Rule 4 — tail 'Compliance' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>keep:0, "Academic Honesty Understanding":3</t>
+          <t>keep:0, "Reference Acknowledgement Recognition":1, "Source Acknowledgement Understanding":1, "Academic Honesty Understanding":1</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -809,17 +809,25 @@
         <v>1</v>
       </c>
       <c r="Z2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Source Acknowledgement</t>
+        </is>
+      </c>
       <c r="AB2" t="b">
         <v>0</v>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Structure Rule 4 — tail 'Compliance' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="AF2" t="b">
         <v>0</v>
       </c>
@@ -860,12 +868,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Academic Integrity Understanding</t>
+          <t>Academic Integrity Recognition</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Supports students by informing them of academic integrity standards and ethical practices.</t>
+          <t>Supports students by providing academic integrity modules that educate on standards and promote ethical practices.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -913,12 +921,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>keep:1, "Academic Integrity Understanding":2</t>
+          <t>keep:0, "Academic Integrity Recognition":3</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -942,13 +950,9 @@
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>vague skill from course description — "Academic Integrity Understanding" uses non-assessable term: {'understanding'}</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -998,7 +1002,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Makes decisions on cases of cheating, plagiarism, and collusion using institutional policies to apply appropriate sanctions.</t>
+          <t>Cheating, plagiarism, and collusion cases using institutional policies to appropriate sanctions.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1047,7 +1051,7 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>keep:2, "Academic Misconduct Determination":1</t>
+          <t>keep:2, "Academic Integrity Decision‑Making":1</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1123,7 +1127,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Supports citation development using reference software to organize sources and ensure accurate referencing.</t>
+          <t>Supports citation management using reference software to organize sources and ensure accurate referencing.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1200,7 +1204,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Reference Management</t>
+          <t>Referencing Skills Development</t>
         </is>
       </c>
       <c r="AB5" t="b">
@@ -1304,12 +1308,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>keep:0, "Collusion Detection":3</t>
+          <t>keep:0, "Collusion Detection":2, "Collusion Recognition":1</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1514,7 +1518,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Students avoid plagiarism by using citation methods and ensuring originality.</t>
+          <t>Avoids plagiarism through citation methods and originality checks.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1562,12 +1566,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>keep:0, "Plagiarism Avoidance":3</t>
+          <t>keep:0, "Plagiarism Avoidance":2, "Citation Management":1</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1638,7 +1642,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Reference Management</t>
+          <t>Referencing Skills Development</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1669,7 +1673,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>citation management; academic writing; APA style; Zotero; bibliography</t>
+          <t>citation management; academic writing; APA style; bibliography; referencing</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1696,7 +1700,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>keep:0, "Reference Management":2, "Referencing Application":1</t>
+          <t>keep:0, "Referencing Skills Development":2, "Reference Acknowledgement":1</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1713,12 +1717,16 @@
         </is>
       </c>
       <c r="Y9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Source Acknowledgement (LLM verified, sim=0.61)</t>
+        </is>
+      </c>
       <c r="AB9" t="b">
         <v>0</v>
       </c>
@@ -1767,7 +1775,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Source Acknowledgement Practice</t>
+          <t>Source Acknowledgement</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1798,7 +1806,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>citation; referencing; bibliography; academic integrity; plagiarism prevention</t>
+          <t>citation; referencing; bibliography; academic integrity; acknowledgement</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1813,15 +1821,19 @@
         </is>
       </c>
       <c r="R10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>keep:0, "Reference Acknowledgement":1, "Source Acknowledgement":1, "Reference Acknowledgement Facilitation":1</t>
+          <t>keep:0, "Source Acknowledgement":2, "Reference Acknowledgement":1</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1838,16 +1850,12 @@
         </is>
       </c>
       <c r="Y10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Reference Management (LLM verified, sim=0.61)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="b">
         <v>0</v>
       </c>
@@ -1901,7 +1909,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Learns about Turnitin as the text‑matching tool used at La Trobe University.</t>
+          <t>Uses Turnitin to support originality.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1945,12 +1953,12 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>keep:1, "Turnitin Similarity Analysis":1, "Turnitin Utilisation":1</t>
+          <t>keep:0, "Turnitin Utilisation":1, "Turnitin Similarity Analysis":1, "Turnitin Similarity Checking":1</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -2021,17 +2029,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Integrity Resource Utilisation</t>
+          <t>Integrity Policy Utilisation</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Locates, selects, and utilises La Trobe's academic integrity information to support proper reference acknowledgement.</t>
+          <t>Locates, selects and utilises La Trobe’s academic integrity information to support correct reference acknowledgement.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>technical</t>
+          <t>domain_knowledge</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2052,7 +2060,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>academic integrity resources; reference acknowledgement; La Trobe policies; information selection; resource utilisation</t>
+          <t>academic integrity policy; information retrieval; reference acknowledgement; La Trobe guidelines; policy utilisation</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2063,7 +2071,7 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Integrity Resource Utilisation</t>
+          <t>Integrity Policy Utilisation</t>
         </is>
       </c>
       <c r="R12" t="b">
@@ -2080,7 +2088,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Locates, selects, and applies La Trobe's academic integrity information to ensure proper reference acknowledgement.</t>
+          <t>Locates, selects and applies La Trobe’s academic integrity information to ensure correct reference acknowledgement.</t>
         </is>
       </c>
       <c r="W12" t="b">
@@ -2088,7 +2096,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>academic integrity resources, reference acknowledgement, La Trobe policies, information selection, resource utilisation</t>
+          <t>academic integrity policy, information retrieval, reference acknowledgement, La Trobe guidelines, policy utilisation</t>
         </is>
       </c>
       <c r="Y12" t="b">
@@ -2152,12 +2160,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cultural Beliefs Evaluation</t>
+          <t>Cultural Attitudes Reflection</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Critically reflects on cultural attitudes, values, and beliefs within hybrid learning settings to inform inclusive practice.</t>
+          <t>Reflects critically on cultural attitudes, values and beliefs within hybrid learning settings to inform inclusive practice.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2183,7 +2191,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>self‑reflection; cultural awareness; values assessment; metacognition; beliefs</t>
+          <t>self‑reflection; cultural awareness; bias analysis; values assessment; attitudes</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2205,12 +2213,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>keep:0, "Cultural Beliefs Evaluation/Cultural Attitudes Evaluation":2, "Cultural Beliefs Reflection":1</t>
+          <t>keep:0, "Cultural Attitudes Reflection":3</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2234,7 +2242,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Cultural Attitudes Reflection</t>
+          <t>Cultural Attitudes Critical Reflection</t>
         </is>
       </c>
       <c r="AB13" t="b">
@@ -2291,12 +2299,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cultural Attitudes Reflection</t>
+          <t>Cultural Attitudes Critical Reflection</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Critically reflects on personal cultural attitudes, values, and beliefs in hybrid learning settings.</t>
+          <t>Reflects critically on personal cultural attitudes, values and beliefs in hybrid learning settings.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2344,12 +2352,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>keep:1, "Cultural Attitudes Reflection":2</t>
+          <t>keep:0, "Cultural Attitudes Critical Reflection":3</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2373,7 +2381,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Cultural Attitudes Analysis</t>
+          <t>Cultural Attitudes Reflection</t>
         </is>
       </c>
       <c r="AB14" t="b">
@@ -2430,12 +2438,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cultural Attitudes Analysis</t>
+          <t>Cultural Attitudes Reflection</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Critically reflects on cultural attitudes, values, and beliefs within hybrid learning environments to inform inclusive practice.</t>
+          <t>Reflects critically on cultural attitudes, values and beliefs within hybrid learning environments to inform inclusive practice.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2461,7 +2469,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>self‑reflection; intercultural competence; values assessment; cultural attitudes; cultural self‑awareness</t>
+          <t>self‑reflection; cultural attitudes; values assessment; intercultural competence; cultural self‑awareness</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2476,15 +2484,19 @@
         </is>
       </c>
       <c r="R15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T15" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>keep:1, "Cultural Attitudes Review":1, "Cultural Attitudes Reflection":1</t>
+          <t>keep:0, "Cultural Attitudes Reflection":3</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2561,7 +2573,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cultural Literacy Development</t>
+          <t>Indigenous Cultural Literacy Development</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2592,7 +2604,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>cultural heritage; intercultural competence; diversity awareness; cultural literacy; cultural studies</t>
+          <t>indigenous cultural literacy; cultural heritage; intercultural competence; diversity awareness; cultural studies</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2607,15 +2619,19 @@
         </is>
       </c>
       <c r="R16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T16" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>keep:2, "Indigenous Cultural Literacy Development":1</t>
+          <t>keep:1, "Indigenous Cultural Literacy Development":2</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2692,7 +2708,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Indigenous Cultural Knowledge</t>
+          <t>Indigenous Culture Respecting</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2723,7 +2739,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Indigenous Australian perspectives; cultural competency; Aboriginal history and customs; reconciliation and cultural protocols; Indigenous knowledge</t>
+          <t>Indigenous Australian perspectives; cultural competency; Aboriginal history and customs; reconciliation and cultural protocols; Indigenous cultural respect</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2738,15 +2754,19 @@
         </is>
       </c>
       <c r="R17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>MIS re-refinement: Structure Rule 4 — tail 'Knowledge' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>keep:0, "Indigenous Cultural Understanding":1, "Indigenous cultural knowledge demonstration":1, "Indigenous Cultural Knowledge Assessment":1</t>
+          <t>keep:2, "Indigenous Culture Understanding":1</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2774,9 +2794,13 @@
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Structure Rule 4 — tail 'Knowledge' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="AF17" t="b">
         <v>0</v>
       </c>
@@ -2823,7 +2847,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Indigenous Customs Comprehension</t>
+          <t>Indigenous Customs Understanding</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2854,7 +2878,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>anthropology; Aboriginal cultural heritage; cross‑cultural competency; Australian Indigenous history; Indigenous customs</t>
+          <t>anthropology; Aboriginal cultural heritage; cross‑cultural competency; Australian Indigenous history; customs</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2869,19 +2893,15 @@
         </is>
       </c>
       <c r="R18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0.9</v>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>keep:0, "Indigenous Customs Comprehension":2, "Indigenous Customs Review":1</t>
+          <t>keep:1, "Indigenous Cultural Recollection":1, "Indigenous Customs Recording":1</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2905,7 +2925,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Indigenous History Recall</t>
+          <t>Indigenous History Detail Recall</t>
         </is>
       </c>
       <c r="AB18" t="b">
@@ -2962,7 +2982,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Indigenous History Recall</t>
+          <t>Indigenous History Detail Recall</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2993,7 +3013,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Indigenous Australia; cultural heritage; oral history; anthropology; historical knowledge</t>
+          <t>Indigenous Australia; cultural heritage; oral history; memory recall; specific detail</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -3008,15 +3028,19 @@
         </is>
       </c>
       <c r="R19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T19" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>MIS re-refinement: Structure Rule 1 — tail 'Recall' is not an action-as-noun; rewrite to end in an action.</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>keep:2, "Indigenous History Recall":1</t>
+          <t>keep:1, "Indigenous History Recall/Indigenous History-Culture Recall":2</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -3033,7 +3057,7 @@
         </is>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="b">
         <v>0</v>
@@ -3044,9 +3068,13 @@
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Structure Rule 1 — tail 'Recall' is not an action-as-noun; rewrite to end in an action.</t>
+        </is>
+      </c>
       <c r="AF19" t="b">
         <v>0</v>
       </c>
@@ -3124,7 +3152,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>indigenous knowledge; traditional ecological knowledge; cultural literacy; community‑based learning; intercultural competence</t>
+          <t>traditional ecological knowledge; cultural literacy; decolonizing curricula; integration; intercultural competence</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -3142,12 +3170,12 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Indigenous Knowledge Incorporation":1</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -3228,7 +3256,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Indigenous Perspectives Recognition</t>
+          <t>Indigenous Perspectives Demonstration</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3259,7 +3287,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>cultural competency; Australian Aboriginal knowledge; decolonisation; reconciliation; recognition</t>
+          <t>cultural competency; Australian Aboriginal knowledge; decolonisation; reconciliation; demonstration</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3277,16 +3305,16 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>MIS re-refinement: Structure Rule 4 — tail 'Awareness' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>keep:0, "Indigenous Perspectives Recognition":2, "Indigenous Perspectives Understanding":1</t>
+          <t>keep:0, "Indigenous Perspectives Appreciation":1, "Indigenous Perspectives Recognition":1, "Indigenous Perspectives Understanding":1</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -3310,7 +3338,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Indigenous Perspectives Appreciation</t>
+          <t>Indigenous Perspectives Acknowledgement</t>
         </is>
       </c>
       <c r="AB21" t="b">
@@ -3318,9 +3346,13 @@
       </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Structure Rule 4 — tail 'Awareness' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="AF21" t="b">
         <v>0</v>
       </c>
@@ -3398,7 +3430,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>cultural sensitivity; cross-cultural communication; diversity awareness; intercultural competence; appreciation</t>
+          <t>cultural sensitivity; cross-cultural communication; diversity awareness; intercultural competence; intercultural appreciation</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -3421,7 +3453,7 @@
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>keep:1, "Intercultural Communication Understanding":1, "Intercultural Communication Valuation":1</t>
+          <t>keep:2, "Intercultural Communication Valuation":1</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3498,7 +3530,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Intercultural Communication</t>
+          <t>Intercultural Communication Understanding</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3529,7 +3561,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>cultural competence; cross-cultural collaboration; global communication; intercultural competence; effective intercultural communication</t>
+          <t>cultural competence; diversity awareness; global communication; intercultural competence; understanding</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -3551,12 +3583,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>keep:0, "Intercultural Communication":2, "Intercultural Communication Understanding":1</t>
+          <t>keep:0, "Intercultural Communication Understanding":3</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3637,7 +3669,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Intercultural Communication Appreciation</t>
+          <t>Intercultural Communication Understanding</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3668,7 +3700,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>cross-cultural competence; cultural awareness; appreciation; diversity and inclusion; intercultural training</t>
+          <t>cross-cultural competence; cultural awareness; diversity and inclusion; intercultural training; intercultural understanding</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3695,7 +3727,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>keep:0, "Intercultural Communication Appreciation":2, "Intercultural Communication Valuation":1</t>
+          <t>keep:0, "Intercultural Communication Understanding":2, "Intercultural Communication Valuation":1</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -3776,7 +3808,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Local Community Appreciation</t>
+          <t>Local Country Appreciation</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3807,7 +3839,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>cultural awareness; regional customs; community engagement; cross‑cultural communication; local appreciation</t>
+          <t>cultural awareness; community engagement; local people; appreciation; country</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -3822,19 +3854,15 @@
         </is>
       </c>
       <c r="R25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.925</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>keep:1, "Local Community Appreciation/Local People Appreciation":2</t>
+          <t>keep:2, "Local People Country Appreciation":1</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3911,7 +3939,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Indigenous Perspectives Appreciation</t>
+          <t>Indigenous Perspectives Acknowledgement</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3942,7 +3970,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Indigenous Australian; cultural competency; reconciliation; perspectives; appreciation</t>
+          <t>Indigenous Australian; cultural competency; reconciliation; acknowledgement; perspectives</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3960,16 +3988,16 @@
         <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>MIS re-refinement: Structure Rule 1 — tail 'Perspectives' is not an action-as-noun; rewrite to end in an action.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>keep:0, "Indigenous Perspectives Appreciation":2, "Indigenous Perspectives Respect":1</t>
+          <t>keep:0, "Indigenous Perspectives Appreciation":1, "Indigenous Perspectives Respect":1, "Indigenous Perspectives Respecting":1</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3993,7 +4021,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Indigenous Perspectives Engagement</t>
+          <t>Indigenous Perspectives Acknowledgement</t>
         </is>
       </c>
       <c r="AB26" t="b">
@@ -4001,9 +4029,13 @@
       </c>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Structure Rule 1 — tail 'Perspectives' is not an action-as-noun; rewrite to end in an action.</t>
+        </is>
+      </c>
       <c r="AF26" t="b">
         <v>0</v>
       </c>
@@ -4050,7 +4082,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Indigenous Perspectives Engagement</t>
+          <t>Indigenous Perspectives Acknowledgement</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4081,7 +4113,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>cultural competency; Indigenous Australian perspectives; intercultural communication; community engagement; respect for Indigenous</t>
+          <t>cultural competency; Indigenous Australian perspectives; intercultural communication; acknowledgement; diversity and inclusion</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4108,7 +4140,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>keep:0, "Indigenous Perspectives Engagement":2, "Indigenous Perspectives Appreciation":1</t>
+          <t>keep:0, "Indigenous Perspectives Acknowledgement":2, "Indigenous Perspectives Respecting":1</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -4128,13 +4160,9 @@
         <v>1</v>
       </c>
       <c r="Z27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>Indigenous Knowledge Integration (LLM verified, sim=0.62)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="b">
         <v>0</v>
       </c>
@@ -4194,7 +4222,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Views the university timetable to see all available subjects and their schedule details.</t>
+          <t>Views the university timetable to locate all available subjects for enrolment.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4220,7 +4248,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>university timetable; subject availability; schedule review; course planning; navigation</t>
+          <t>university timetable; subject selection; schedule review; academic planning; navigation</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -4248,7 +4276,7 @@
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Locates and reviews the university timetable to identify all available subjects and their schedule details.</t>
+          <t>Locates and reviews the university timetable to identify all available subjects for enrolment.</t>
         </is>
       </c>
       <c r="W28" t="b">
@@ -4256,11 +4284,11 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>university timetable, subject availability, schedule review, course planning, navigation</t>
+          <t>university timetable, subject selection, schedule review, academic planning, online portal</t>
         </is>
       </c>
       <c r="Y28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="b">
         <v>0</v>
@@ -4325,7 +4353,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Explains university fees and associated costs clearly to students, ensuring they understand financial obligations.</t>
+          <t>Explains university fee structures and associated costs clearly to students and stakeholders.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4343,15 +4371,15 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>practical</t>
+          <t>theoretical</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>university fees; cost breakdown; student finance; tuition charges; fee structure</t>
+          <t>university fees; cost breakdown; tuition charges; student expenses; fee structure</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -4369,7 +4397,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4379,7 +4407,7 @@
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Explains university fees and associated costs clearly to students, ensuring they understand financial obligations.</t>
+          <t>Explains university fee structures and associated costs clearly to students and stakeholders.</t>
         </is>
       </c>
       <c r="W29" t="b">
@@ -4387,7 +4415,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>university fees, cost breakdown, student finance, tuition charges, financial obligations</t>
+          <t>university fees, cost breakdown, tuition charges, student expenses, financial information</t>
         </is>
       </c>
       <c r="Y29" t="b">
@@ -4456,7 +4484,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Assists international students by explaining cultural resources, navigating services, and fostering inclusive engagement.</t>
+          <t>Assists international students in understanding and engaging with Indigenous cultural literacy content and requirements.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4478,11 +4506,11 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>international students; cultural orientation; support services; academic integration; student wellbeing</t>
+          <t>international students; cultural orientation; support services; academic integration; cultural awareness</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -4500,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4510,7 +4538,7 @@
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Assists international students by explaining cultural resources, navigating services, and fostering inclusive engagement.</t>
+          <t>Assists international students in understanding and engaging with Indigenous cultural literacy content and requirements.</t>
         </is>
       </c>
       <c r="W30" t="b">
@@ -4518,7 +4546,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>international students, cultural orientation, support services, academic integration, student wellbeing</t>
+          <t>international students, cultural orientation, support services, academic integration, cultural awareness</t>
         </is>
       </c>
       <c r="Y30" t="b">
@@ -4577,7 +4605,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Suitable authentication mechanisms in cryptographic technique contexts in communication and cybersecurity.</t>
+          <t>Describes suitable authentication mechanisms in contexts of cryptographic techniques in communication and cybersecurity.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4702,7 +4730,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Explains foundational mathematical concepts and constructions underlying cryptographic methods in theoretical analyses.</t>
+          <t>Explains foundational mathematical concepts and constructions underlying cryptographic methods.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4755,7 +4783,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>keep:0, "Cryptographic Methods Explanation/basic cryptographic methods explanation":3</t>
+          <t>keep:0, "Cryptographic Methods Explanation":3</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -4764,7 +4792,7 @@
         </is>
       </c>
       <c r="W32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4831,7 +4859,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Applies cryptographic techniques to solve straightforward security challenges in practical tasks.</t>
+          <t>Employs cryptographic techniques to solve straightforward security challenges in practical tasks.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4889,7 +4917,7 @@
         </is>
       </c>
       <c r="W33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4947,12 +4975,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cryptographic Technique Identification</t>
+          <t>Cryptographic Technique Summarisation</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Identifies diverse cryptographic methods in theoretical context.</t>
+          <t>Identifies diverse cryptographic methods in theoretical contexts.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4978,7 +5006,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>cryptography; encryption algorithms; hash functions; public‑key cryptography; cryptographic technique</t>
+          <t>cryptography; encryption algorithms; public‑key cryptography; technique; summarisation</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -4993,19 +5021,15 @@
         </is>
       </c>
       <c r="R34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
-          <t>keep:1, "Cryptographic Technique Identification":2</t>
+          <t>keep:1, "Cryptographic Technique Identification":1, "Cryptographic Technique Summarisation":1</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -5025,13 +5049,9 @@
         <v>1</v>
       </c>
       <c r="Z34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Cryptographic Technique Context Identification</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="b">
         <v>0</v>
       </c>
@@ -5076,7 +5096,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cryptographic Technique Context Identification</t>
+          <t>Cryptographic Application Context Identification</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5107,7 +5127,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>cryptographic techniques; encryption protocols; digital signatures; key management; public key infrastructure</t>
+          <t>cryptographic application; cryptographic context; encryption protocols; digital signatures; key management</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -5134,7 +5154,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>keep:0, "Cryptographic Technique Context Identification":2, "Cryptographic Application Description":1</t>
+          <t>keep:0, "Cryptographic Application Context Identification":2, "Cryptographic Application Context Description":1</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -5206,7 +5226,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Explains foundational mathematical concepts and constructions that support cryptographic techniques in theoretical contexts.</t>
+          <t>Explains foundational mathematical concepts and constructions underlying cryptographic techniques in theoretical contexts.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5232,7 +5252,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>mathematical principles; number theory; discrete mathematics; modular arithmetic; abstract algebra</t>
+          <t>cryptography; number theory; discrete mathematics; modular arithmetic; mathematical principles</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -5247,19 +5267,15 @@
         </is>
       </c>
       <c r="R36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>keep:0, "Mathematical Principles Explanation":3</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -5268,7 +5284,7 @@
         </is>
       </c>
       <c r="W36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -5331,7 +5347,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>AES private-key algorithms.</t>
+          <t>Evaluates AES private-key algorithms to assess security properties and identify potential vulnerabilities.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5357,7 +5373,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>symmetric cryptography; AES; encryption; private; key management</t>
+          <t>private key; encryption; AES; block cipher; key management</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -5375,12 +5391,12 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
-          <t>keep:1, "Private Key Encryption Assessment":1, "Private Key Encryption Evaluation":1</t>
+          <t>keep:0, "Private Key Encryption Analysis":1, "Private Key Encryption Identification":1, "Private Key Encryption Summarisation":1</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -5389,7 +5405,7 @@
         </is>
       </c>
       <c r="W37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -5447,12 +5463,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Public Key Encryption Analysis</t>
+          <t>Public Key Encryption Identification</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Evaluates RSA public‑key schemes by mathematically analyzing key generation and security properties.</t>
+          <t>RSA public‑key schemes, including key generation and security properties.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5478,7 +5494,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>cryptography; RSA algorithm; asymmetric encryption; public key systems; security protocols</t>
+          <t>cryptography; RSA algorithm; asymmetric encryption; public key; security protocols</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -5493,15 +5509,19 @@
         </is>
       </c>
       <c r="R38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T38" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>keep:2, "Public Key Encryption Identification":1</t>
+          <t>keep:0, "Public Key Encryption Identification":2, "Public Key Encryption Summarisation":1</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -5510,7 +5530,7 @@
         </is>
       </c>
       <c r="W38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -5568,7 +5588,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Secure Transmission Context Description</t>
+          <t>Secure Transmission Description</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5599,7 +5619,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>cryptography; secure communication; encryption; secure transmission; application context</t>
+          <t>cryptography; secure communication; encryption; transmission; cybersecurity</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -5614,19 +5634,15 @@
         </is>
       </c>
       <c r="R39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>keep:0, "Secure Transmission Context Description/Secure Transmission Description":2, "Secure Transmission Documentation":1</t>
+          <t>keep:2, "Secure Transmission Description":1</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -5697,12 +5713,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cyber Defence Practice Review</t>
+          <t>Cyber Defence Practices Evaluation</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Knows organization-wide cyber defence strategies and tailors controls to hybrid environments.</t>
+          <t>Tailors controls to hybrid environments based on current cyber defence practices.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5728,7 +5744,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>risk assessment; threat intelligence; incident response planning; defense-in-depth; cyber defence practice</t>
+          <t>risk assessment; threat intelligence; incident response planning; defense-in-depth; cyber defence practices</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -5755,7 +5771,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>keep:0, "Cyber Defence Practice Review":2, "Cyber Defence Practice Evaluation":1</t>
+          <t>keep:0, "Cyber Defence Practices Evaluation/Cyber Defence Practice Evaluation":2, "Cyber Defence Practice Review":1</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -5775,9 +5791,13 @@
         <v>1</v>
       </c>
       <c r="Z40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Cybersecurity Fundamentals Learning</t>
+        </is>
+      </c>
       <c r="AB40" t="b">
         <v>0</v>
       </c>
@@ -5826,12 +5846,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cybersecurity Fundamentals Understanding</t>
+          <t>Cybersecurity Fundamentals Learning</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Core cybersecurity concepts for current defensive practices for organizations.</t>
+          <t>Core cybersecurity concepts describe current defensive practices for organizations.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5857,7 +5877,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>information security; cyber defense; network security; cybersecurity; fundamentals</t>
+          <t>information security; cyber defense; network security; cybersecurity fundamentals; learning</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -5872,15 +5892,19 @@
         </is>
       </c>
       <c r="R41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>keep:0, "Cybersecurity Fundamentals Comprehension":1, "Cyber Defence Familiarisation":1, "Cybersecurity Fundamentals Review":1</t>
+          <t>keep:1, "Cybersecurity Fundamentals Learning":2</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -5900,13 +5924,9 @@
         <v>1</v>
       </c>
       <c r="Z41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Cyber Defence Practice Review</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="b">
         <v>0</v>
       </c>
@@ -5960,7 +5980,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Investigates, evaluates and applies up-to-date cybersecurity tools in hybrid environments to mitigate threats.</t>
+          <t>Evaluates up-to-date cybersecurity tools in hybrid environments to mitigate threats.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5986,7 +6006,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>threat detection; SIEM; intrusion prevention; cybersecurity; technology</t>
+          <t>threat detection; vulnerability assessment; security architecture; cybersecurity; technology</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -6004,12 +6024,12 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>keep:1, "Cybersecurity Technology Application":1, "Cybersecurity Technology Assessment":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -6080,12 +6100,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Firewall Configuration Management</t>
+          <t>Firewall Configuration</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Identifies firewalls and common threat-identification technologies to mitigate network risks.</t>
+          <t>Identifies threats using common technologies to mitigate network risks with firewalls.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6111,7 +6131,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>network security; firewall policies; access control lists; firewall configuration; threat mitigation</t>
+          <t>network security; firewall policies; access control lists; Cisco ASA; firewall configuration</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -6126,15 +6146,19 @@
         </is>
       </c>
       <c r="R43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>keep:0, "Firewall Technology Introduction":1, "Firewall Technology Evaluation":1, "Firewall Utilisation":1</t>
+          <t>keep:0, "Firewall Configuration":2, "Firewall Introduction":1</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -6214,7 +6238,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Identifies honeypot deployment strategies using common threat-identification technologies to mitigate attacks.</t>
+          <t>Identifies threats using common technologies and deploys honeypot strategies to mitigate attacks.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -6338,7 +6362,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Incident Response Description</t>
+          <t>Incident Response Process Description</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6369,7 +6393,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>threat intelligence; vulnerability assessment; SIEM; incident response; incident handling playbooks</t>
+          <t>threat intelligence; vulnerability assessment; security operations center; SIEM; incident handling playbooks</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -6396,7 +6420,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Description":3</t>
+          <t>keep:0, "Incident Response Process Description/Incident Response Description":3</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -6413,7 +6437,7 @@
         </is>
       </c>
       <c r="Y45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="b">
         <v>1</v>
@@ -6471,7 +6495,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Intrusion Detection System Analysis</t>
+          <t>Intrusion Detection Analysis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6502,7 +6526,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>network security; IDS; SIEM; anomaly detection; intrusion detection</t>
+          <t>network security; IDS; SIEM; anomaly detection; threat mitigation</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -6517,19 +6541,15 @@
         </is>
       </c>
       <c r="R46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
-          <t>keep:0, "Intrusion Detection System Analysis":2, "Intrusion Detection System Introduction":1</t>
+          <t>keep:0, "Intrusion Detection Introduction":1, "Intrusion Detection System Evaluation":1, "Intrusion Detection System Analysis":1</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -6546,7 +6566,7 @@
         </is>
       </c>
       <c r="Y46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="b">
         <v>0</v>
@@ -6600,12 +6620,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cybersecurity Technology Application</t>
+          <t>Cybersecurity Technologies Application</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Investigates and evaluates cybersecurity tools, applying them to hybrid systems.</t>
+          <t>Evaluates and applies cybersecurity tools for hybrid systems to mitigate risk.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6631,7 +6651,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>cybersecurity; threat detection; vulnerability assessment; security controls; cybersecurity technology</t>
+          <t>cybersecurity; threat detection; vulnerability assessment; technologies; application</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -6658,7 +6678,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>keep:0, "Cybersecurity Technology Application":2, "Cybersecurity Technology Evaluation":1</t>
+          <t>keep:0, "Cybersecurity Technologies Application/Cybersecurity Technology Application":2, "Cybersecurity Technology Evaluation":1</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -6733,12 +6753,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Secure Programming Implementation</t>
+          <t>Secure Software Design</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Designs secure design patterns within collaborative team projects.</t>
+          <t>Designs secure software using patterns within collaborative team projects.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6764,7 +6784,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>secure coding; threat modeling; static analysis; secure programming; DevSecOps</t>
+          <t>secure coding; threat modeling; static analysis; DevSecOps; software design</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -6786,12 +6806,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>keep:0, "Secure Programming Implementation/Secure Programming Practice Implementation":2, "Secure Software Design Implementation":1</t>
+          <t>keep:0, "Secure Software Design":3</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -6920,7 +6940,7 @@
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>keep:1, "Secure Software Design":1, "Secure Software Design Implementation":1</t>
+          <t>keep:1, "Secure Software Design Implementation":1, "Secure Software Design Application":1</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -7121,7 +7141,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Investigates, evaluates, and applies emerging cybersecurity technologies within hybrid security policies.</t>
+          <t>Investigates, evaluates, and applies emerging cybersecurity technologies to hybrid security policies.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -7169,12 +7189,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>keep:0, "Cybersecurity Technology Evaluation":3</t>
+          <t>keep:0, "Cybersecurity Technology Evaluation":2, "Cybersecurity Technologies Application":1</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -7249,12 +7269,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Team-based Secure Coding</t>
+          <t>Secure Software Design</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Designs secure design patterns and code reviews in hybrid teams throughout development.</t>
+          <t>Designs secure software using design patterns and code reviews in hybrid teams.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -7280,7 +7300,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>secure software design; threat modeling; code review; team collaboration; secure coding</t>
+          <t>secure software design; threat modeling; code review; OWASP guidelines; working in teams</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -7295,15 +7315,19 @@
         </is>
       </c>
       <c r="R52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="T52" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>keep:2, "Secure Coding Implementation":1</t>
+          <t>keep:0, "Secure Software Design":2, "Software Design Collaboration":1</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -7378,12 +7402,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Threat Identification</t>
+          <t>Threat and Vulnerability Identification</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Describes systematic threat and vulnerability identification and incident response procedures within hybrid cybersecurity environments.</t>
+          <t>Describes systematic threat and vulnerability identification and initiates incident response procedures within hybrid cybersecurity environments.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -7436,7 +7460,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>keep:0, "Threat Identification":2, "Threat Identification Assessment":1</t>
+          <t>keep:0, "Threat and Vulnerability Identification/Threat Identification":2, "Threat Identification Process Description":1</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -7511,7 +7535,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Vulnerability Assessment</t>
+          <t>Vulnerability Identification Description</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7542,7 +7566,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>threat modeling; vulnerability scanning; risk assessment; incident response; vulnerability identification</t>
+          <t>threat modeling; vulnerability scanning; risk assessment; incident response; cybersecurity frameworks</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -7569,7 +7593,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>keep:0, "Vulnerability Assessment":2, "Vulnerability Identification":1</t>
+          <t>keep:0, "Vulnerability Identification Description/Vulnerability Assessment Description":2, "Vulnerability Assessment":1</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -7586,7 +7610,7 @@
         </is>
       </c>
       <c r="Y54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="b">
         <v>1</v>
@@ -7645,12 +7669,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Collaborative Data Analysis</t>
+          <t>Data Analysis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Engages in joint data analysis in hybrid labs with peers.</t>
+          <t>Joint data analysis in hybrid labs with peers.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -7676,7 +7700,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>teamwork; statistical software; lab collaboration; interdisciplinary research; hybrid learning</t>
+          <t>teamwork; laboratory classes; lab collaboration; interdisciplinary research; hybrid learning</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -7691,15 +7715,19 @@
         </is>
       </c>
       <c r="R55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T55" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>keep:1, "Data Analysis":1, "Data Analysis Collaboration":1</t>
+          <t>keep:0, "Data Analysis":3</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -7716,7 +7744,7 @@
         </is>
       </c>
       <c r="Y55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z55" t="b">
         <v>0</v>
@@ -7771,7 +7799,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Data-based Critical Thinking Application</t>
+          <t>Data-based Critical Thinking</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -7802,7 +7830,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>critical thinking; evidence-based reasoning; data analysis; logical inference; problem solving</t>
+          <t>evidence-based reasoning; data analysis; logical inference; problem solving; critical thinking</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -7824,12 +7852,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>keep:0, "Data-Based Critical Thinking Application/Critical Thinking Application":3</t>
+          <t>keep:0, "Data-Based Critical Thinking":2, "Data-Based Critical Thinking Application":1</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -7901,7 +7929,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Data-based Evidence Evaluation</t>
+          <t>Data Evidence Evaluation</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7932,7 +7960,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>critical thinking; data literacy; evidence assessment; statistical reasoning; data-based evidence</t>
+          <t>critical thinking; data literacy; evidence assessment; statistical reasoning; information verification</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -7947,19 +7975,15 @@
         </is>
       </c>
       <c r="R57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
-          <t>keep:1, "Data-Based Evidence Evaluation/Data Evidence Evaluation":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -7976,16 +8000,12 @@
         </is>
       </c>
       <c r="Y57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>Media Data Evaluation (LLM verified, sim=0.61)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="b">
         <v>0</v>
       </c>
@@ -8214,12 +8234,12 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
-          <t>keep:2, "Data Transformation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -8452,7 +8472,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>descriptive statistics; data visualization; numeric summarization; statistical summary; interpretation</t>
+          <t>descriptive statistics; data visualization; graphical analysis; numeric summarization; interpretation</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -8479,7 +8499,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>keep:0, "Statistical Summary Interpretation/Data Summary Interpretation":3</t>
+          <t>keep:0, "Statistical Summary Interpretation":3</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -8555,12 +8575,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Media Data Evaluation</t>
+          <t>Media Data Conclusions Evaluation</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Reports media-reported data conclusions, cross‑checking sources and methodology in hybrid learning settings.</t>
+          <t>Reports on media data conclusions in hybrid learning settings.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -8586,7 +8606,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>fact‑checking; data literacy; media; misinformation detection; source verification</t>
+          <t>fact‑checking; data literacy; statistical evaluation; media; conclusions</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -8604,16 +8624,16 @@
         <v>1</v>
       </c>
       <c r="S62" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t>MIS re-refinement: Structure Rule 1 — tail 'Critique' is not an action-as-noun; rewrite to end in an action.</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>keep:0, "Media Data Evaluation":3</t>
+          <t>keep:0, "Data Conclusions Evaluation":1, "Data Conclusion Assessment":1, "Media Data Critiquing":1</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -8641,9 +8661,13 @@
       </c>
       <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>Structure Rule 1 — tail 'Critique' is not an action-as-noun; rewrite to end in an action.</t>
+        </is>
+      </c>
       <c r="AF62" t="b">
         <v>0</v>
       </c>
@@ -8685,12 +8709,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Numeracy Interpretation</t>
+          <t>Numeracy Analysis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Interprets quantitative data using core numeracy techniques across business, scientific, and professional contexts.</t>
+          <t>Core numeracy techniques to quantitative data across business, scientific, and professional contexts.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -8716,7 +8740,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>quantitative reasoning; data interpretation; statistical analysis; mathematical modelling; numeracy</t>
+          <t>quantitative reasoning; data interpretation; statistical analysis; mathematical modeling; numeracy</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -8731,19 +8755,15 @@
         </is>
       </c>
       <c r="R63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
-          <t>keep:0, "Numeracy Interpretation":2, "Statistical Summary Interpretation":1</t>
+          <t>keep:0, "Statistical Summary Interpretation":1, "Numeracy Application":1, "Numerical Data Interpretation":1</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -8846,7 +8866,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>probability theory; decision analysis; Monte Carlo simulation; calculation; risk assessment</t>
+          <t>probability theory; statistical inference; decision analysis; Monte Carlo simulation; probability calculation</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -8864,12 +8884,12 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Probability Calculation":1</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -8972,7 +8992,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>probability reasoning; cognitive bias; statistical misconceptions; decision-making errors; concept inventories</t>
+          <t>probability reasoning; cognitive bias; statistical misconceptions; decision-making errors; probability misconception</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -8987,19 +9007,15 @@
         </is>
       </c>
       <c r="R65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr">
         <is>
-          <t>keep:0, "Probability Misconception Identification":3</t>
+          <t>keep:1, "Probability Misconception Identification":1, "Probability Misconception Discussion":1</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -9016,7 +9032,7 @@
         </is>
       </c>
       <c r="Y65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z65" t="b">
         <v>0</v>
@@ -9102,7 +9118,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>descriptive statistics; data visualization; summary metrics; statistical reporting; interpretation</t>
+          <t>descriptive statistics; data visualization; summary metrics; statistical interpretation; statistical reporting</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -9202,7 +9218,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Explains functions of various input, output, and storage devices.</t>
+          <t>Explains functions of various input, output, and storage devices in system design.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -9246,12 +9262,12 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Hardware Device Identification":1</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -9283,9 +9299,13 @@
         </is>
       </c>
       <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>Structure Rule 1 — tail 'Fundamentals' is not an action-as-noun; rewrite to end in an action.</t>
+        </is>
+      </c>
       <c r="AF67" t="b">
         <v>0</v>
       </c>
@@ -9358,7 +9378,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>operating systems; hardware architecture; CPU processing; input/output management; computer operation</t>
+          <t>operating systems; hardware architecture; CPU processing; computer operation; computer</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -9401,13 +9421,9 @@
         <v>1</v>
       </c>
       <c r="Z68" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>Software Operation Fundamentals</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA68" t="inlineStr"/>
       <c r="AB68" t="b">
         <v>0</v>
       </c>
@@ -9506,12 +9522,12 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr">
         <is>
-          <t>keep:2, "Data Processing Demonstration":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -9614,7 +9630,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>HTML; markup language; web design; CSS; JavaScript</t>
+          <t>markup language; HTML; web design; CSS; JavaScript</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -9636,12 +9652,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>keep:0, "HTML Development/HTML Web Development":3</t>
+          <t>keep:1, "HTML Development":2</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -9718,7 +9734,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Interprets IT component roles to support data delivery to end users.</t>
+          <t>Interprets IT component roles to explain how they support the delivery of data to end users.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -9744,7 +9760,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>information systems; data dissemination; information architecture; delivery; interpretation</t>
+          <t>information systems; data dissemination; information architecture; data delivery; interpretation</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -9766,12 +9782,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>keep:0, "Information Delivery Interpretation":2, "Component Role Interpretation":1</t>
+          <t>keep:0, "Information Delivery Interpretation":3</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -10004,7 +10020,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>troubleshooting; HTML; networking; system administration; technical support</t>
+          <t>troubleshooting; networking; system administration; technical support; problem solving</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -10027,7 +10043,7 @@
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr">
         <is>
-          <t>keep:2, "IT Issue Resolution":1</t>
+          <t>keep:2, "Problem Solving":1</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -10044,7 +10060,7 @@
         </is>
       </c>
       <c r="Y73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z73" t="b">
         <v>0</v>
@@ -10104,7 +10120,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>LAN and WAN devices, IP schemes, and connectivity in campus networks.</t>
+          <t>LAN and WAN devices, IP schemes, and connectivity troubleshooting in campus networks.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -10130,7 +10146,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>network configuration; networking; TCP/IP; routing; Cisco</t>
+          <t>networking; TCP/IP; routing; VLAN; network configuration</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -10153,7 +10169,7 @@
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr">
         <is>
-          <t>keep:1, "LAN/WAN Network Description":1, "LAN/WAN Network Survey":1</t>
+          <t>keep:1, "Computer Network Configuration":1, "LAN/WAN Network Installation":1</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -10225,7 +10241,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>IT Application</t>
+          <t>Practical IT Application</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -10256,7 +10272,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>information technology; applied computing; software application; field‑specific software; technical problem solving</t>
+          <t>information technology; applied computing; hands‑on labs; practical application; field‑specific software</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -10271,19 +10287,15 @@
         </is>
       </c>
       <c r="R75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr">
         <is>
-          <t>keep:0, "IT Application":3</t>
+          <t>keep:2, "IT Application":1</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -10386,7 +10398,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>relational model; database; schema design; entity-relationship modelling; conceptualisation</t>
+          <t>relational model; database; normalization; schema design; entity-relationship modeling</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -10413,7 +10425,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>keep:0, "Relational Database Conceptualisation/Database Conceptualisation":3</t>
+          <t>keep:0, "Database Conceptualisation":3</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -10485,12 +10497,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Software Operation Fundamentals</t>
+          <t>Computer Operation Instruction</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Core computer operation principles to troubleshoot basic software tasks.</t>
+          <t>Core computer operation principles are used to troubleshoot basic software tasks.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -10516,7 +10528,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>computer architecture; operating system basics; hardware-software interaction; system software concepts; computer operations</t>
+          <t>computer architecture; operating system basics; hardware-software interaction; computer operation; instruction</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -10531,15 +10543,19 @@
         </is>
       </c>
       <c r="R77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S77" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T77" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>keep:1, "Computer Operation Training":1, "Computer Operations Understanding":1</t>
+          <t>keep:0, "Computer Operation Instruction":2, "Computer Operations Training":1</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -10559,17 +10575,17 @@
         <v>1</v>
       </c>
       <c r="Z77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA77" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Computer System Operation</t>
+        </is>
+      </c>
       <c r="AB77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>vague skill from course description — "Software Operation Fundamentals" uses non-assessable term: {'fundamentals'}</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -10772,7 +10788,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>secure coding; OWASP; threat modeling; DevSecOps; application security</t>
+          <t>secure coding; OWASP; threat modeling; vulnerability scanning; application security</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -10790,12 +10806,12 @@
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr">
         <is>
-          <t>keep:2, "Application Security Implementation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -10920,12 +10936,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>keep:0, "Cryptography Solution Investigation":2, "Cryptography Solution Design":1</t>
+          <t>keep:0, "Cryptography Solution Investigation":3</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -11051,7 +11067,7 @@
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr">
         <is>
-          <t>keep:2, "Cyber Risk Management Evaluation":1</t>
+          <t>keep:2, "Cyber Risk Management Application":1</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -11128,7 +11144,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Familiarises stakeholders with basic cybersecurity principles and best practices.</t>
+          <t>Familiarises hybrid stakeholders with basic cybersecurity principles, best practices and compliance.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -11154,7 +11170,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>information security; risk assessment; security best practices; cybersecurity; principles</t>
+          <t>information security; risk assessment; security best practices; cybersecurity principles; security awareness</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -11176,12 +11192,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>keep:0, "Cybersecurity Principles Familiarisation":2, "Cybersecurity Principles Review":1</t>
+          <t>keep:0, "Cybersecurity Principles Familiarisation":3</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -11284,7 +11300,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>digital forensics; forensic investigation; EnCase; memory analysis; evidence collection</t>
+          <t>digital forensics; investigation; EnCase; memory analysis; evidence collection</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -11299,15 +11315,19 @@
         </is>
       </c>
       <c r="R83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S83" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T83" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>keep:2, "Digital Forensics Investigation":1</t>
+          <t>keep:1, "Digital Forensics Investigation":2</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -11379,7 +11399,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cyber Risk Management Comparison</t>
+          <t>Digital Risk Evaluation</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -11410,7 +11430,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>cyber risk; risk assessment; security frameworks; vulnerability analysis; comparison</t>
+          <t>cyber risk; threat modeling; risk assessment; digital risk; vulnerability analysis</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -11425,19 +11445,15 @@
         </is>
       </c>
       <c r="R84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr">
         <is>
-          <t>keep:0, "Cyber Risk Management Comparison":2, "Cyber Risk Evaluation":1</t>
+          <t>keep:0, "Cyber Risk Management Comparison":1, "Cyber Risk Management":1, "Cyber Risk Management Application":1</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -11513,12 +11529,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ethical Legal Compliance</t>
+          <t>Ethical Legal Practices Implementation</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Ethical and legal standards guide practices to ensure compliance in academic settings.</t>
+          <t>Ethical and legal standards to practices and compliance in academic settings.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -11544,7 +11560,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>regulatory; governance; legal standards; ethical standards; compliance</t>
+          <t>practices; governance; risk management; legal standards; ethical standards</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -11559,15 +11575,19 @@
         </is>
       </c>
       <c r="R85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S85" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T85" t="inlineStr"/>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>MIS re-refinement: Structure Rule 4 — tail 'Compliance' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>keep:1, "Ethical Legal Practice Compliance":1, "Ethical Legal Practice Assessment":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -11595,9 +11615,13 @@
       </c>
       <c r="AC85" t="inlineStr"/>
       <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>Structure Rule 4 — tail 'Compliance' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="AF85" t="b">
         <v>0</v>
       </c>
@@ -11670,7 +11694,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>cybersecurity; incident response; log analysis; SIEM; digital forensics</t>
+          <t>incident response; threat hunting; log analysis; SIEM; digital forensics</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -11688,12 +11712,12 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Incident Response Analysis":1</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -11765,7 +11789,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Information Security Assurance</t>
+          <t>Information Security Management</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -11796,7 +11820,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>information security; data privacy; encryption; risk management; assurance</t>
+          <t>information security; data privacy; confidentiality; encryption; risk management</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -11818,12 +11842,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t>MIS re-refinement: Structure Rule 4 — tail 'Assurance' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>keep:0, "Information System Assurance/Information Security Assurance":3</t>
+          <t>keep:1, "Information Security Assurance":2</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -11851,9 +11875,13 @@
       </c>
       <c r="AC87" t="inlineStr"/>
       <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>Structure Rule 4 — tail 'Assurance' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="AF87" t="b">
         <v>0</v>
       </c>
@@ -11900,7 +11928,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Demonstrates foundation skills by identifying malware samples during lab exercises.</t>
+          <t>Demonstrates identification of malware samples using basic analysis tools during lab exercises.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -11926,7 +11954,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>malware analysis; reverse engineering; YARA rules; threat intelligence; malware identification</t>
+          <t>malware analysis; reverse engineering; sandbox testing; YARA rules; malware identification</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -12030,7 +12058,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Secures firewalls and access controls to protect campus networks per policy.</t>
+          <t>Secures firewalls and access controls to secure campus networks per policy.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -12056,7 +12084,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>firewall; intrusion detection; access control; network segmentation; configuration</t>
+          <t>firewall; intrusion detection; access control; network segmentation; network configuration</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -12074,12 +12102,12 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Network Security Implementation":1</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -12156,7 +12184,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Investigates security issues and solutions efficiently with team members.</t>
+          <t>Investigates security issues with team members to identify solutions.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -12200,12 +12228,12 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.9</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr">
         <is>
-          <t>keep:1, "Solution Investigation":1, "Team Based Security Investigation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -12330,12 +12358,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>keep:1, "Vulnerability Mitigation":2</t>
+          <t>keep:0, "Vulnerability Mitigation":3</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -12412,7 +12440,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Investigates web applications and vulnerabilities to enhance security.</t>
+          <t>Investigates web applications to enhance security as a team member.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -12438,7 +12466,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>web application security; vulnerability scanning; penetration testing; OWASP; investigation</t>
+          <t>web application security; vulnerability scanning; penetration testing; risk analysis; investigation</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -12542,7 +12570,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Analyzes emerging cybersecurity practices, regulations and standards to evaluate their impact on digital security.</t>
+          <t>Independently analyses emerging cybersecurity practices, regulations and standards to assess their impact on digital security.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -12564,11 +12592,11 @@
         </is>
       </c>
       <c r="M93" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>emerging cybersecurity practices; cybersecurity regulations; digital security implications; regulatory standards; cybersecurity analysis</t>
+          <t>emerging practices; cybersecurity regulations; security standards; cybersecurity standards; standards evaluation</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -12586,7 +12614,7 @@
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -12596,7 +12624,7 @@
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
-          <t>Analyzes emerging cybersecurity practices, regulations and standards to evaluate their impact on digital security.</t>
+          <t>Independently analyses emerging cybersecurity practices, regulations and standards to assess their impact on digital security.</t>
         </is>
       </c>
       <c r="W93" t="b">
@@ -12604,7 +12632,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>emerging cybersecurity practices, regulatory standards, digital security implications, standards evaluation, cybersecurity analysis</t>
+          <t>emerging practices, cybersecurity regulations, security standards, digital security implications, standards evaluation</t>
         </is>
       </c>
       <c r="Y93" t="b">
@@ -12664,7 +12692,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>IP Addressing Principles</t>
+          <t>IP Addressing Learning</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -12695,7 +12723,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>subnetting; IPv4; IPv6; addressing; principles</t>
+          <t>subnetting; IPv4; IPv6; addressing; learning</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -12710,15 +12738,19 @@
         </is>
       </c>
       <c r="R94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
       </c>
-      <c r="T94" t="inlineStr"/>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>MIS re-refinement: Structure Rule 1 — tail 'Principles' is not an action-as-noun; rewrite to end in an action.</t>
+        </is>
+      </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>keep:0, "IP Addressing Principle Analysis":1, "IP Addressing Principle Comprehension":1, "IP Addressing Principle Assessment":1</t>
+          <t>keep:0, "IP Addressing Principle Learning":1, "IP Addressing Principle Comprehension":1, "IP Addressing Understanding":1</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -12746,9 +12778,13 @@
       </c>
       <c r="AC94" t="inlineStr"/>
       <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>Structure Rule 1 — tail 'Principles' is not an action-as-noun; rewrite to end in an action.</t>
+        </is>
+      </c>
       <c r="AF94" t="b">
         <v>0</v>
       </c>
@@ -12791,7 +12827,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>LAN Ethernet Evolution</t>
+          <t>LAN Evolution</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -12822,7 +12858,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Ethernet standards; IEEE 802.3; CSMA/CD; network topology; evolution</t>
+          <t>Ethernet standards; IEEE 802.3; LAN evolution; network topology; switching technologies</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -12849,7 +12885,7 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>keep:0, "LAN Ethernet Evolution Description":2, "LAN Ethernet Evolution Analysis":1</t>
+          <t>keep:1, "LAN Evolution Description":2</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -13080,7 +13116,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>OSI model; network design; TCP/IP stack; packet forwarding; layer interaction</t>
+          <t>OSI model; interaction; network design; TCP/IP stack; packet forwarding</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -13189,7 +13225,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Applies appropriate physical network standards based on specific scenario requirements.</t>
+          <t>Applies appropriate physical network standards for specific scenario requirements.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -13233,7 +13269,7 @@
         <v>1</v>
       </c>
       <c r="S98" t="n">
-        <v>0.925</v>
+        <v>0.9</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -13262,9 +13298,13 @@
         <v>0</v>
       </c>
       <c r="Z98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA98" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>Network Physical Standards Application</t>
+        </is>
+      </c>
       <c r="AB98" t="b">
         <v>0</v>
       </c>
@@ -13346,7 +13386,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>network physical standards; topology design; scenario analysis; network architecture; application</t>
+          <t>network physical standards; topology design; capacity planning; scenario analysis; network architecture</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -13390,16 +13430,12 @@
         </is>
       </c>
       <c r="Y99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>Network Physical Standards Application</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="b">
         <v>0</v>
       </c>
@@ -13581,7 +13617,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Packet Lifecycle Understanding</t>
+          <t>Packet Lifecycle Exploration</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -13612,7 +13648,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>networking; TCP/IP; packet flow; routing; packet lifecycle</t>
+          <t>exploration; TCP/IP; packet flow; routing; lifecycle</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -13627,15 +13663,19 @@
         </is>
       </c>
       <c r="R101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S101" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T101" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>keep:1, "Data Packet Lifecycle Exploration":1, "Packet Lifecycle Comprehension":1</t>
+          <t>keep:1, "Packet Lifecycle Exploration":2</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -13659,13 +13699,9 @@
       </c>
       <c r="AA101" t="inlineStr"/>
       <c r="AB101" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>vague skill from course description — "Packet Lifecycle Understanding" uses non-assessable term: {'understanding'}</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC101" t="inlineStr"/>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -13717,7 +13753,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Compares network protocol suites against the OSI model regarding layer functions and interoperability.</t>
+          <t>Compares network protocol suites against the OSI model, focusing on layer functions and interoperability.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -13743,7 +13779,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>OSI model; protocol stack; TCP/IP; layered architecture; protocol suite comparison</t>
+          <t>OSI model; protocol stack; TCP/IP; comparison; suite</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -13761,12 +13797,12 @@
         <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr">
         <is>
-          <t>keep:2, "TCP/IP Suite Comparison":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -13786,13 +13822,9 @@
         <v>1</v>
       </c>
       <c r="Z102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>TCP/IP Protocol Analysis (LLM verified, sim=0.67)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA102" t="inlineStr"/>
       <c r="AB102" t="b">
         <v>0</v>
       </c>
@@ -13843,7 +13875,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Simple Network Topology Development</t>
+          <t>Simple Network Topology Design</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -13874,7 +13906,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>networking; LAN architecture; VLAN configuration; network topology; simple network</t>
+          <t>networking; LAN architecture; routing protocols; VLAN configuration; simple network topology</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -13889,19 +13921,15 @@
         </is>
       </c>
       <c r="R103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr">
         <is>
-          <t>keep:0, "Simple Network Topology Development/Network Topology Development":2, "Simple Network Topology Management":1</t>
+          <t>keep:1, "Simple Network Topology Development":1, "Simple Network Topology Management":1</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -14023,12 +14051,12 @@
         <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr">
         <is>
-          <t>keep:2, "Static Routing Implementation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -14048,9 +14076,13 @@
         <v>1</v>
       </c>
       <c r="Z104" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA104" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>Simple Network Topology Design (LLM verified, sim=0.79)</t>
+        </is>
+      </c>
       <c r="AB104" t="b">
         <v>0</v>
       </c>
@@ -14101,7 +14133,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>TCP/IP Protocol Analysis</t>
+          <t>TCP/IP Protocol Suite Comparison</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -14132,7 +14164,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>OSI model; network layers; packet sniffing; Wireshark; network protocol suite</t>
+          <t>OSI model; network layers; network protocol suite; comparison; packet sniffing</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -14147,15 +14179,19 @@
         </is>
       </c>
       <c r="R105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S105" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T105" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>keep:2, "TCP/IP Protocol Comparison":1</t>
+          <t>keep:0, "TCP/IP Protocol Suite Comparison":3</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -14172,12 +14208,16 @@
         </is>
       </c>
       <c r="Y105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA105" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>Protocol Suite Comparison</t>
+        </is>
+      </c>
       <c r="AB105" t="b">
         <v>0</v>
       </c>
@@ -14232,7 +14272,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Abstract data type principles related to software solutions.</t>
+          <t>Abstract data type principles to data structures for software solutions.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -14281,7 +14321,7 @@
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr">
         <is>
-          <t>keep:1, "Abstract Data Type Relation":1, "ADT Principle Analysis":1</t>
+          <t>keep:1, "ADT Principles Analysis":1, "Abstract Data Type Evaluation":1</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -14731,12 +14771,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Exception Handling Implementation</t>
+          <t>Exception Handling</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Selects try-catch blocks to check runtime errors and design program stability.</t>
+          <t>Designs try-catch blocks to check runtime errors and select program stability.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -14762,7 +14802,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>error handling; try-catch; fault tolerance; exception handling; software robustness</t>
+          <t>error handling; try-catch; fault tolerance; debugging; exception handling</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -14777,15 +14817,19 @@
         </is>
       </c>
       <c r="R110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S110" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="T110" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Exception Handling":2, "Exception Handling Execution":1</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -14888,7 +14932,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>object-oriented programming; inheritance; class hierarchy; polymorphism; UML</t>
+          <t>inheritance; object-oriented programming; class hierarchy; code reuse; UML</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -14906,12 +14950,12 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr">
         <is>
-          <t>keep:0, "Inheritance Application":1, "Inheritance Utilisation":1, "Inheritance Implementation":1</t>
+          <t>keep:2, "Inheritance Implementation":1</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -14988,7 +15032,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Designs functional Java applications by selecting and checking code for assigned projects.</t>
+          <t>Designs Java applications by selecting code and checking functionality for assigned projects.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -15014,7 +15058,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>object-oriented; JDK; java; programming; software development</t>
+          <t>object-oriented; JDK; java; software development; programming</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -15266,7 +15310,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>design patterns; encapsulation; inheritance; UML modeling; object-oriented approach</t>
+          <t>object-oriented approach; comparison; encapsulation; inheritance; UML modeling</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -15293,7 +15337,7 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>keep:0, "Object-Oriented Approach Comparison/Object-Oriented Design Comparison":3</t>
+          <t>keep:0, "Object-Oriented Approach Comparison":3</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -15396,7 +15440,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>object-oriented programming; software design; algorithm development; problem solving; UML modeling</t>
+          <t>object-oriented programming; design patterns; software design; problem solving; real-life problem</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -15418,12 +15462,12 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>keep:0, "Object-Oriented Problem Solving":3</t>
+          <t>keep:0, "Object-Oriented Problem Solving/Object‑Oriented Problem Solving":2, "Object‑Oriented Method Application":1</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -15526,7 +15570,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>software modeling; object-oriented design; class diagram; sequence diagram; UML diagramming</t>
+          <t>software modeling; object-oriented design; class diagram; sequence diagram; diagramming</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -15626,7 +15670,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Selects code changes using version control systems to track revisions and checks with teammates.</t>
+          <t>Selects code changes using version control systems to track revisions.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -15751,12 +15795,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Flowchart Development</t>
+          <t>Flowchart Design</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Uses clear algorithmic flowcharts using simple drawing techniques to map program logic.</t>
+          <t>Uses simple drawing techniques for clear algorithmic flowcharts mapping program logic.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -15804,12 +15848,12 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>keep:0, "Flowchart Development":3</t>
+          <t>keep:0, "Flowchart Design":2, "Flowchart Designing":1</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
@@ -15934,12 +15978,12 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>keep:0, "Problem Decomposition":2, "Problem Analysis":1</t>
+          <t>keep:0, "Problem Decomposition":3</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
@@ -15963,7 +16007,7 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>Problem Decomposition</t>
+          <t>Problem Decomposition Analysis</t>
         </is>
       </c>
       <c r="AB119" t="b">
@@ -16046,7 +16090,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>ETL; data pipelines; batch processing; Hadoop; Spark</t>
+          <t>ETL; data pipelines; scheduled jobs; Spark; batch data processing</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -16061,19 +16105,15 @@
         </is>
       </c>
       <c r="R120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr">
         <is>
-          <t>keep:1, "Batch Data Processing":2</t>
+          <t>keep:2, "Batch Data Processing Solving":1</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
@@ -16093,13 +16133,9 @@
         <v>1</v>
       </c>
       <c r="Z120" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>Data Structure Utilisation (LLM verified, sim=0.74)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA120" t="inlineStr"/>
       <c r="AB120" t="b">
         <v>0</v>
       </c>
@@ -16203,7 +16239,7 @@
       <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr">
         <is>
-          <t>keep:1, "Computational Solution Design":1, "Computational Solution Development":1</t>
+          <t>keep:1, "Computational Solution Development":1, "Computational Solution Designing":1</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
@@ -16275,7 +16311,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Control Structure Implementation</t>
+          <t>Control Structure Application</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -16306,7 +16342,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>control flow; conditional logic; loop structures; algorithmic design; program structure</t>
+          <t>control flow; conditional logic; loop structures; algorithmic design; programming fundamentals</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -16321,15 +16357,19 @@
         </is>
       </c>
       <c r="R122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S122" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="T122" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Control Structure Application":2</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
@@ -16346,7 +16386,7 @@
         </is>
       </c>
       <c r="Y122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="b">
         <v>0</v>
@@ -16401,7 +16441,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Data Processing Analysis</t>
+          <t>Data Processing Problem Analysis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -16432,7 +16472,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>data analysis; data modeling; algorithmic processing; information extraction; data science</t>
+          <t>data analysis; data modelling; algorithmic processing; data science; data processing problem</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -16447,15 +16487,19 @@
         </is>
       </c>
       <c r="R123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S123" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="T123" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Data Processing Problem Analysis/Data Processing Analysis":3</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
@@ -16472,7 +16516,7 @@
         </is>
       </c>
       <c r="Y123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z123" t="b">
         <v>0</v>
@@ -16576,7 +16620,7 @@
         <v>1</v>
       </c>
       <c r="S124" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -16585,7 +16629,7 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>keep:2, "Data Structure Utilisation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
@@ -16657,7 +16701,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Problem Decomposition</t>
+          <t>Problem Decomposition Analysis</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -16703,19 +16747,15 @@
         </is>
       </c>
       <c r="R125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr">
         <is>
-          <t>keep:1, "Problem Decomposition":2</t>
+          <t>keep:2, "Problem Decomposition":1</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
@@ -16818,7 +16858,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>control flow; loops; conditionals; algorithmic thinking; programming constructs</t>
+          <t>control flow; loops; conditionals; software application; programming constructs</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -16840,12 +16880,12 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>keep:0, "Programming Constructs Application/Programming Fundamentals Application":2, "Programming Fundamentals Understanding":1</t>
+          <t>keep:0, "Programming Constructs Application/Programming Fundamentals Application":3</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
@@ -16948,7 +16988,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>scripting; software development; programming; data processing; Python libraries</t>
+          <t>scripting; software development; programming; Python libraries; automation</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -17174,7 +17214,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Evaluates Australian and international law, examining statutes and cases to select appropriate legal practice.</t>
+          <t>Evaluates Australian and international law, examining statutes and cases to select legal practice approaches.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -17218,12 +17258,12 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr">
         <is>
-          <t>keep:2, "Law Comparative Analysis":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
@@ -17326,7 +17366,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>policy analysis; regulatory compliance; effectiveness assessment; governance; legal framework</t>
+          <t>policy analysis; legal research; effectiveness assessment; governance; legal framework</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -17348,12 +17388,12 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>keep:0, "Legal Framework Evaluation":2, "Law and Policy Evaluation":1</t>
+          <t>keep:0, "Legal Framework Evaluation":3</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
@@ -17377,7 +17417,7 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>Law Policy Effectiveness Evaluation</t>
+          <t>Legal Framework Evaluation</t>
         </is>
       </c>
       <c r="AB130" t="b">
@@ -17434,7 +17474,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Describes cyberspace security issues associated with the use of the cyberspace across hybrid environments.</t>
+          <t>Describes cyberspace security issues across hybrid environments.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -17483,7 +17523,7 @@
       <c r="T131" t="inlineStr"/>
       <c r="U131" t="inlineStr">
         <is>
-          <t>keep:0, "Cyberspace Security Issue Assessment":1, "Cybersecurity Issues Analysis":1, "Security Issue Analysis":1</t>
+          <t>keep:0, "Security Issue Analysis":1, "Security Issue Description":1, "Cyberspace Security Issues Analysis":1</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
@@ -17559,7 +17599,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Effectiveness Evaluation</t>
+          <t>Law Policy Effectiveness Evaluation</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -17590,7 +17630,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>policy analysis; cybersecurity law; regulatory impact assessment; compliance evaluation; effectiveness</t>
+          <t>policy analysis; cybersecurity law; regulatory impact assessment; compliance evaluation; effectiveness evaluation</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -17605,15 +17645,19 @@
         </is>
       </c>
       <c r="R132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S132" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>keep:0, "Legal Framework Effectiveness Evaluation":1, "Laws Policies Evaluation":1, "Cyberspace Policy Effectiveness Evaluation":1</t>
+          <t>keep:0, "Law Policy Effectiveness Evaluation/Cyberspace Law Effectiveness Evaluation":2, "Legal Effectiveness Evaluation":1</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
@@ -17637,7 +17681,7 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>Policy Effectiveness Assessment</t>
+          <t>Policy Effectiveness Evaluation</t>
         </is>
       </c>
       <c r="AB132" t="b">
@@ -17689,7 +17733,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Law Policy Effectiveness Evaluation</t>
+          <t>Legal Framework Evaluation</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -17720,7 +17764,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>policy analysis; industry self‑regulation; legal frameworks; governance and risk assessment; effectiveness</t>
+          <t>policy analysis; regulatory compliance; industry self‑regulation; legal frameworks; governance and risk assessment</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -17747,7 +17791,7 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>keep:0, "Law Policy Effectiveness Evaluation/Law Policy Evaluation":2, "Legal Framework Evaluation":1</t>
+          <t>keep:0, "Legal Framework Evaluation/Legal Framework Effectiveness Evaluation":2, "Regulation Effectiveness Evaluation":1</t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
@@ -17764,14 +17808,14 @@
         </is>
       </c>
       <c r="Y133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z133" t="b">
         <v>1</v>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>Policy Evaluation (LLM verified, sim=0.65)</t>
+          <t>Policy Effectiveness Evaluation (LLM verified, sim=0.65)</t>
         </is>
       </c>
       <c r="AB133" t="b">
@@ -17828,7 +17872,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Pays attention to legal, political and technological viewpoints in hybrid settings to inform comprehensive perspectives.</t>
+          <t>Pays attention to legal, political and technological perspectives in hybrid settings to inform comprehensive understanding.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -17854,7 +17898,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>legal analysis; policy studies; technology assessment; cross-disciplinary research; perspective synthesis</t>
+          <t>legal analysis; policy studies; technology assessment; interdisciplinary perspective; synthesis</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -17877,7 +17921,7 @@
       <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr">
         <is>
-          <t>keep:2, "Interdisciplinary Perspective Integration":1</t>
+          <t>keep:2, "Interdisciplinary Perspective Analysis":1</t>
         </is>
       </c>
       <c r="V134" t="inlineStr">
@@ -17897,13 +17941,9 @@
         <v>1</v>
       </c>
       <c r="Z134" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>Stakeholder Perspective Analysis</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA134" t="inlineStr"/>
       <c r="AB134" t="b">
         <v>0</v>
       </c>
@@ -17953,12 +17993,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Australian International Law Comparison</t>
+          <t>Law Comparison</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Evaluating Australian and international legal frameworks to inform policy recommendations.</t>
+          <t>Evaluates Australian and international legal frameworks to inform policy recommendations.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -18006,12 +18046,12 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>keep:0, "Australian International Law Comparison/Law Comparison":2, "Australian-International Law Comparison":1</t>
+          <t>keep:0, "Law Comparison/Australian International Law Comparison":3</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
@@ -18092,7 +18132,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Analyses cyberspace regulations and legal frameworks to support policy compliance and strategy.</t>
+          <t>Analyses cyberspace regulations and legal frameworks to ensure policy compliance and strategy.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -18136,12 +18176,12 @@
         <v>0</v>
       </c>
       <c r="S136" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr">
         <is>
-          <t>keep:1, "Laws and Policies Analysis":1, "Law and Policy Analysis":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V136" t="inlineStr">
@@ -18161,9 +18201,13 @@
         <v>0</v>
       </c>
       <c r="Z136" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA136" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>Legal Framework Identification (LLM verified, sim=0.85)</t>
+        </is>
+      </c>
       <c r="AB136" t="b">
         <v>0</v>
       </c>
@@ -18262,12 +18306,12 @@
         <v>0</v>
       </c>
       <c r="S137" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr">
         <is>
-          <t>keep:0, "Laws and Policies Identification":1, "Law Policy Identification":1, "Legal Framework Identification":1</t>
+          <t>keep:2, "Law and Policy Identification":1</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
@@ -18287,13 +18331,9 @@
         <v>1</v>
       </c>
       <c r="Z137" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>Legal Framework Identification</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="b">
         <v>0</v>
       </c>
@@ -18348,7 +18388,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Analyses cyber‑law compliance by analysing relevant statutes and policies across online and offline environments.</t>
+          <t>Analyses cyber‑law compliance through relevant statutes and policies across online and offline environments.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -18396,12 +18436,12 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>keep:0, "Legal Framework Analysis":3</t>
+          <t>keep:0, "Legal Framework Analysis":2, "Cyberspace Law Analysis":1</t>
         </is>
       </c>
       <c r="V138" t="inlineStr">
@@ -18477,7 +18517,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Policy Effectiveness Assessment</t>
+          <t>Policy Impact Assessment</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -18508,7 +18548,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>cyberspace security; cybersecurity policy; regulatory compliance; policy effectiveness; cyber governance</t>
+          <t>cybersecurity policy; risk assessment; policy effectiveness; cyber governance; policy impact</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -18523,19 +18563,15 @@
         </is>
       </c>
       <c r="R139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr">
         <is>
-          <t>keep:0, "Law Policy Effectiveness Assessment/Policy Effectiveness Assessment":3</t>
+          <t>keep:0, "Law Policy Impact Assessment":1, "Law and Policy Evaluation":1, "Policy Effectiveness Assessment":1</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
@@ -18559,7 +18595,7 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>Policy Evaluation (LLM verified, sim=0.79)</t>
+          <t>Law Policy Effectiveness Evaluation</t>
         </is>
       </c>
       <c r="AB139" t="b">
@@ -18611,7 +18647,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Policy Evaluation</t>
+          <t>Policy Effectiveness Evaluation</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -18642,7 +18678,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>policy analysis; regulatory impact assessment; evidence‑based policymaking; legislative evaluation; applicability of laws</t>
+          <t>policy analysis; regulatory impact assessment; evidence‑based policymaking; legislative evaluation; effectiveness</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -18741,12 +18777,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Legal Framework Identification</t>
+          <t>Law and Policy Identification</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Identifies applicable cyberspace laws and policies in hybrid environments to support regulatory compliance.</t>
+          <t>Identifies applicable cyberspace laws and policies in hybrid environments.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -18772,7 +18808,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>cybersecurity law; policy analysis; risk assessment; compliance frameworks; information security governance</t>
+          <t>cybersecurity law; applicable laws; policy analysis; compliance frameworks; information security governance</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -18799,7 +18835,7 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>keep:0, "Legal Framework Identification":2, "Laws and Policies Identification":1</t>
+          <t>keep:0, "Law and Policy Identification":2, "Regulatory Compliance Identification":1</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
@@ -18816,14 +18852,14 @@
         </is>
       </c>
       <c r="Y141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z141" t="b">
         <v>1</v>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>Law and Policy Analysis (LLM verified, sim=0.85)</t>
+          <t>Legal Framework Identification</t>
         </is>
       </c>
       <c r="AB141" t="b">
@@ -18880,7 +18916,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Describes cyberspace security issues, including threats and mitigation strategies in hybrid environments.</t>
+          <t>Describes cyberspace security issues, describing threats and mitigation strategies in hybrid environments.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -18928,12 +18964,12 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>keep:0, "Security Issue Description":2, "Security Issue Analysis":1</t>
+          <t>keep:0, "Security Issue Description":3</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
@@ -19036,7 +19072,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>stakeholder mapping; legal analysis; political risk assessment; technology assessment; expert perspective</t>
+          <t>stakeholder mapping; legal analysis; political risk assessment; technology assessment; perspective analysis</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -19054,12 +19090,12 @@
         <v>0</v>
       </c>
       <c r="S143" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr">
         <is>
-          <t>keep:2, "Stakeholder Perspective Analysis":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
@@ -19079,9 +19115,13 @@
         <v>1</v>
       </c>
       <c r="Z143" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA143" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>Interdisciplinary Perspective Synthesis</t>
+        </is>
+      </c>
       <c r="AB143" t="b">
         <v>0</v>
       </c>
@@ -19127,7 +19167,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Information Availability Assurance</t>
+          <t>Information Availability Maintenance</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -19158,7 +19198,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>information security; confidentiality; integrity; assurance; availability</t>
+          <t>information security; confidentiality; integrity; availability; maintenance</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -19176,16 +19216,16 @@
         <v>1</v>
       </c>
       <c r="S144" t="n">
-        <v>0.9</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>MIS re-refinement: Structure Rule 4 — tail 'Assurance' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>keep:0, "Information Availability Assurance/Information Assurance":2, "Information Security Management":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
@@ -19209,7 +19249,7 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>Information Assurance</t>
+          <t>Integrity Assurance</t>
         </is>
       </c>
       <c r="AB144" t="b">
@@ -19217,9 +19257,13 @@
       </c>
       <c r="AC144" t="inlineStr"/>
       <c r="AD144" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE144" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>Structure Rule 4 — tail 'Assurance' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="AF144" t="b">
         <v>0</v>
       </c>
@@ -19262,7 +19306,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Ensures compliance by ensuring policies protect confidentiality, integrity, and availability of organizational information.</t>
+          <t>Ensures compliance through policies that protect confidentiality, integrity, and availability of organizational information.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -19310,12 +19354,12 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>MIS re-refinement: Structure Rule 4 — tail 'Assurance' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
         </is>
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>keep:1, "Information Assurance/Organisational Information Assurance":2</t>
+          <t>keep:0, "Confidentiality Integrity Availability Assurance":2, "Information Security Assurance":1</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
@@ -19339,7 +19383,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>Information Assurance</t>
+          <t>Information Availability Maintenance</t>
         </is>
       </c>
       <c r="AB145" t="b">
@@ -19347,9 +19391,13 @@
       </c>
       <c r="AC145" t="inlineStr"/>
       <c r="AD145" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE145" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>Structure Rule 4 — tail 'Assurance' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="AF145" t="b">
         <v>0</v>
       </c>
@@ -19387,7 +19435,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Data Maintenance Evaluation</t>
+          <t>Data Maintenance Compliance Evaluation</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -19418,7 +19466,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>data governance; information security; privacy policy; risk management; data maintenance</t>
+          <t>data governance; information security; data maintenance; risk management; audit compliance</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -19445,7 +19493,7 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>keep:0, "Data Maintenance Evaluation":3</t>
+          <t>keep:0, "Data Maintenance Compliance Evaluation":3</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
@@ -19517,7 +19565,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Data Security Concept Description</t>
+          <t>Data Security Concepts Description</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -19548,7 +19596,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>confidentiality; integrity; concept; description; information assurance</t>
+          <t>confidentiality; integrity; access control; information assurance; data security concepts</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -19570,12 +19618,12 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>keep:0, "Data Security Concept Description/Data Security Concepts Description":2, "Data Security Conceptualisation":1</t>
+          <t>keep:0, "Data Security Concepts Description/Data Security Concept Description":3</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
@@ -19678,7 +19726,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>security policies; data governance; risk assessment; information ethics; ethical practice</t>
+          <t>security policies; data governance; compliance; information ethics; ethical practice</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -19721,13 +19769,9 @@
         <v>1</v>
       </c>
       <c r="Z148" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>Security Policy Evaluation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA148" t="inlineStr"/>
       <c r="AB148" t="b">
         <v>0</v>
       </c>
@@ -19778,7 +19822,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Describes classification schemes for information assets according to sensitivity and regulatory requirements.</t>
+          <t>Describes classification schemes for information assets in line with sensitivity and regulatory requirements.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -19804,7 +19848,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>data classification; information security; asset sensitivity; risk assessment; governance</t>
+          <t>data classification; information security; asset sensitivity; risk assessment; information assets</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -19826,12 +19870,12 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>keep:1, "Information Assets Classification":2</t>
+          <t>keep:0, "Information Assets Classification":3</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
@@ -19848,7 +19892,7 @@
         </is>
       </c>
       <c r="Y149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z149" t="b">
         <v>0</v>
@@ -19904,7 +19948,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Describes data security concepts and assurance frameworks to support organizational protection strategies.</t>
+          <t>Describes data security concepts and assurance frameworks, describing organizational protection strategies.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -19930,7 +19974,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>data security; information assurance principles; cybersecurity; access control; encryption</t>
+          <t>data security; access control; encryption; information assurance; principles</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -19952,12 +19996,12 @@
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>keep:0, "Information Assurance Principles Description":2, "Data Security Concept Description":1</t>
+          <t>keep:0, "Information Assurance Principles Description/Information Assurance Concept Description":3</t>
         </is>
       </c>
       <c r="V150" t="inlineStr">
@@ -20025,7 +20069,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Information Assurance</t>
+          <t>Integrity Assurance</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -20056,7 +20100,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>information security; compliance management; confidentiality; CIA triad; information assurance</t>
+          <t>information security; compliance management; confidentiality; information assurance; CIA triad</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -20071,19 +20115,15 @@
         </is>
       </c>
       <c r="R151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr">
         <is>
-          <t>keep:1, "Information Assurance":2</t>
+          <t>keep:2, "Information Assurance":1</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
@@ -20103,17 +20143,25 @@
         <v>1</v>
       </c>
       <c r="Z151" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA151" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>Security Controls Implementation (LLM verified, sim=0.64)</t>
+        </is>
+      </c>
       <c r="AB151" t="b">
         <v>0</v>
       </c>
       <c r="AC151" t="inlineStr"/>
       <c r="AD151" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE151" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>Structure Rule 4 — tail 'Assurance' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="AF151" t="b">
         <v>0</v>
       </c>
@@ -20151,12 +20199,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Risk Analysis</t>
+          <t>Threat Vulnerability Risk Analysis</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Identifies and analyses comprehensive threat and vulnerability assessments on hybrid information systems.</t>
+          <t>Identifies and analyses threats and vulnerabilities in hybrid information systems to protect organisational information systems.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -20182,7 +20230,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>threat modeling; vulnerability assessment; risk assessment; information security governance; information systems</t>
+          <t>cybersecurity; threat modeling; vulnerability assessment; risk assessment; information systems</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -20204,12 +20252,12 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>keep:1, "Risk Analysis/Threat Vulnerability Risk Analysis":2</t>
+          <t>keep:0, "Threat Vulnerability Risk Analysis":3</t>
         </is>
       </c>
       <c r="V152" t="inlineStr">
@@ -20281,7 +20329,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Security Risk Mitigation</t>
+          <t>Security Controls Implementation</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -20312,7 +20360,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>security risk assessment; technical controls; vulnerability management; risk mitigation; risk analysis methodology</t>
+          <t>security risk assessment; technical controls; vulnerability management; information security governance; security controls</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -20339,7 +20387,7 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>keep:0, "Security Risk Mitigation/Risk Mitigation":2, "Risk Mitigation Planning":1</t>
+          <t>keep:0, "Security Controls Implementation":2, "Security Controls Application":1</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
@@ -20363,7 +20411,7 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>Security Controls Implementation (LLM verified, sim=0.80)</t>
+          <t>Security Controls Implementation</t>
         </is>
       </c>
       <c r="AB153" t="b">
@@ -20416,7 +20464,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Prevalent organizational security challenges through systematic analysis of theoretical frameworks.</t>
+          <t>Prevalent organizational security challenges are examined through systematic analysis of theoretical frameworks.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -20538,7 +20586,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Applies technical and security controls to safeguard organizational information systems.</t>
+          <t>Applies appropriate technical and security controls to safeguard organizational information systems.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -20582,12 +20630,12 @@
         <v>0</v>
       </c>
       <c r="S155" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Security Controls Implementation":1</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
@@ -20704,7 +20752,7 @@
         <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr">
@@ -20729,9 +20777,13 @@
         <v>0</v>
       </c>
       <c r="Z156" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA156" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>Data Maintenance Compliance Evaluation</t>
+        </is>
+      </c>
       <c r="AB156" t="b">
         <v>0</v>
       </c>
@@ -20782,7 +20834,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Identifies and analyses comprehensive threat, vulnerability and risk assessments on organisational information systems within hybrid environments.</t>
+          <t>Identifies and analyses comprehensive threats, vulnerabilities, and risks on organizational information systems within hybrid environments.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -20808,7 +20860,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>risk assessment; vulnerability assessment; threat modeling; information security; information systems</t>
+          <t>risk assessment; vulnerability assessment; threat modeling; information systems; information security</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -20830,12 +20882,12 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>keep:0, "Threat and Vulnerability Analysis/Threat Vulnerability Risk Analysis":3</t>
+          <t>keep:0, "Threat Vulnerability Risk Analysis":2, "Security Risk Analysis":1</t>
         </is>
       </c>
       <c r="V157" t="inlineStr">
@@ -20859,7 +20911,7 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>Threat Vulnerability Risk Assessment</t>
+          <t>Threat Vulnerability Risk Analysis</t>
         </is>
       </c>
       <c r="AB157" t="b">
@@ -20907,12 +20959,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Threat Vulnerability Risk Assessment</t>
+          <t>Threat Vulnerability Risk Analysis</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Identifies and analyses threats to organisational information systems through comprehensive vulnerability assessments across hybrid environments.</t>
+          <t>Identifies and analyses threats, vulnerabilities and risks affecting organisational information systems.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -20965,7 +21017,7 @@
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>keep:0, "Threat Vulnerability Risk Assessment":2, "Security Risk Assessment":1</t>
+          <t>keep:0, "Threat Vulnerability Risk Analysis":2, "Security Risk Analysis":1</t>
         </is>
       </c>
       <c r="V158" t="inlineStr">
@@ -21092,7 +21144,7 @@
       <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr">
         <is>
-          <t>keep:1, "Communication Strategy Development":1, "Communication Policy Alignment":1</t>
+          <t>keep:2, "Communication Strategy Development":1</t>
         </is>
       </c>
       <c r="V159" t="inlineStr">
@@ -21165,7 +21217,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Risk Management Strategy Development</t>
+          <t>Cost‑effective Risk Management</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -21196,7 +21248,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>risk assessment; mitigation strategies; cost optimization; cost‑benefit analysis; risk management strategies</t>
+          <t>risk assessment; mitigation strategies; cost optimisation; cost-benefit analysis; cost-effective risk management</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -21211,19 +21263,15 @@
         </is>
       </c>
       <c r="R160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr">
         <is>
-          <t>keep:0, "Risk Management Strategy Development/Risk Management Development/Cost‑Effective Risk Management Development":3</t>
+          <t>keep:2, "Cost‑Effective Risk Management Planning":1</t>
         </is>
       </c>
       <c r="V160" t="inlineStr">
@@ -21243,13 +21291,9 @@
         <v>1</v>
       </c>
       <c r="Z160" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>Risk Management Strategy Development</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA160" t="inlineStr"/>
       <c r="AB160" t="b">
         <v>0</v>
       </c>
@@ -21300,7 +21344,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cross-cultural Communication</t>
+          <t>Diverse Environment Communication</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -21346,15 +21390,19 @@
         </is>
       </c>
       <c r="R161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S161" t="n">
-        <v>0</v>
-      </c>
-      <c r="T161" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>keep:0, "Cultural Communication Coordination":1, "Cross-Cultural Communication Facilitation":1, "Diverse Environment Communication":1</t>
+          <t>keep:0, "Diverse Environment Communication":2, "High-Level Communication":1</t>
         </is>
       </c>
       <c r="V161" t="inlineStr">
@@ -21427,12 +21475,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cybercrime Model Analysis</t>
+          <t>Cybercrime Business Model Analysis</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Analyses cybercrime business models and global threats, integrating human factor analysis to examine attack viability.</t>
+          <t>Analyses cybercrime business models and global threats, integrating human factor analysis to analyse attack viability.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -21458,7 +21506,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>threat modeling; human factors; cyber threat intelligence; attack vector analysis; cybercrime</t>
+          <t>threat modeling; human factors; cyber threat intelligence; attack vector analysis; cybercrime business models</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -21558,12 +21606,12 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Cybersecurity Culture Development</t>
+          <t>Cybersecurity Culture Strategy Development</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Develops a comprehensive cyber security culture, education and engagement strategy within the organisational context.</t>
+          <t>Develops a comprehensive cyber security culture, education and engagement strategy within the organisation.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -21589,7 +21637,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>security awareness training; employee engagement; cyber hygiene; phishing simulation; cyber security culture</t>
+          <t>security awareness training; employee engagement; cyber hygiene; phishing simulation; cybersecurity</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -21611,12 +21659,12 @@
       </c>
       <c r="T163" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>keep:0, "Cybersecurity Culture Development":3</t>
+          <t>keep:1, "Cybersecurity Culture Strategy Development":2</t>
         </is>
       </c>
       <c r="V163" t="inlineStr">
@@ -21720,7 +21768,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>cost‑benefit analysis; financial modeling; cybersecurity economics; human factors valuation; economic impact</t>
+          <t>cost‑benefit analysis; financial modeling; cybersecurity economics; economic impact; human factors valuation</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -21738,12 +21786,12 @@
         <v>0</v>
       </c>
       <c r="S164" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T164" t="inlineStr"/>
       <c r="U164" t="inlineStr">
         <is>
-          <t>keep:2, "Human Factors Investment Assessment":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V164" t="inlineStr">
@@ -21821,7 +21869,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Promotes hybrid access policies by considering digital divides, cultural norms, and empowerment factors.</t>
+          <t>Promotes equitable access policies by considering digital divides, cultural norms, and empowerment factors.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -21978,7 +22026,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>critical thinking; decision analysis; feedback evaluation; collaborative assessment; reflective judgment</t>
+          <t>critical thinking; feedback evaluation; collaborative assessment; reflective judgment; evaluative judgement</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -21996,12 +22044,12 @@
         <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr">
         <is>
-          <t>keep:2, "Evaluation Assessment":1</t>
+          <t>keep:1, "Professional Evaluation":1, "Judgement Evaluation":1</t>
         </is>
       </c>
       <c r="V166" t="inlineStr">
@@ -22018,7 +22066,7 @@
         </is>
       </c>
       <c r="Y166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z166" t="b">
         <v>0</v>
@@ -22074,7 +22122,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Psychological Factors Analysis</t>
+          <t>Human Behaviour Analysis</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -22127,12 +22175,12 @@
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>keep:0, "Psychological Factors Analysis":3</t>
+          <t>keep:0, "Human Behaviour Analysis":2, "Psychological Factors Analysis":1</t>
         </is>
       </c>
       <c r="V167" t="inlineStr">
@@ -22152,13 +22200,9 @@
         <v>0</v>
       </c>
       <c r="Z167" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA167" t="inlineStr">
-        <is>
-          <t>Psychological Factors Analysis</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA167" t="inlineStr"/>
       <c r="AB167" t="b">
         <v>0</v>
       </c>
@@ -22240,7 +22284,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>leadership; influence; organizational culture; security awareness communication; information security policy</t>
+          <t>organizational culture; information security policy; security awareness communication; leadership; influence</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -22371,7 +22415,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>conflict resolution; persuasive communication; mediation techniques; cross‑cultural negotiation; facilitation</t>
+          <t>facilitation; persuasive communication; mediation techniques; cross‑cultural negotiation; conflict resolution</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -22516,12 +22560,12 @@
         <v>0</v>
       </c>
       <c r="S170" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T170" t="inlineStr"/>
       <c r="U170" t="inlineStr">
         <is>
-          <t>keep:2, "Psychological Factors Analysis":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V170" t="inlineStr">
@@ -22625,7 +22669,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>risk assessment; mitigation planning; cost‑benefit analysis; risk management strategies; enterprise risk framework</t>
+          <t>risk assessment; mitigation planning; cost‑benefit analysis; enterprise risk framework; risk management strategies</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -22647,12 +22691,12 @@
       </c>
       <c r="T171" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>keep:0, "Risk Management Strategy Development":2, "Risk Management Strategy Proposal":1</t>
+          <t>keep:0, "Risk Management Strategy Development":3</t>
         </is>
       </c>
       <c r="V171" t="inlineStr">
@@ -22672,9 +22716,13 @@
         <v>1</v>
       </c>
       <c r="Z171" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA171" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>Cost‑effective Risk Management</t>
+        </is>
+      </c>
       <c r="AB171" t="b">
         <v>0</v>
       </c>
@@ -22730,7 +22778,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Develops hybrid security strategies for practice safeguards and organizational sustainability objectives.</t>
+          <t>Develops hybrid security strategies that incorporate practice safeguards and organisational sustainability objectives.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -22756,7 +22804,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>risk management; organisational resilience; sustainability governance; security policy development; secure practice</t>
+          <t>risk management; organisational resilience; sustainability governance; security policy development; security practices</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -22771,19 +22819,15 @@
         </is>
       </c>
       <c r="R172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S172" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T172" t="inlineStr"/>
       <c r="U172" t="inlineStr">
         <is>
-          <t>keep:0, "Secure Practice Strategy Development/Secure Practices Strategy Development":3</t>
+          <t>keep:2, "Secure Practice Strategy Development":1</t>
         </is>
       </c>
       <c r="V172" t="inlineStr">
@@ -22861,7 +22905,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Delivers hybrid team-building sessions using evaluative judgement and communication to support diverse members.</t>
+          <t>Delivers hybrid team-building sessions using evaluative judgement and communication to engage diverse members.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -22905,12 +22949,12 @@
         <v>0</v>
       </c>
       <c r="S173" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Team Building Facilitation":1</t>
         </is>
       </c>
       <c r="V173" t="inlineStr">
@@ -22982,7 +23026,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Ad‑hoc Network Protection</t>
+          <t>Ad‑hoc Network Securing</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -23013,7 +23057,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>wireless ad hoc networks; secure routing protocols; MAC layer security; key management; network protection</t>
+          <t>wireless ad hoc networks; secure routing protocols; MAC layer security; key management; broadcast authentication</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -23031,16 +23075,16 @@
         <v>1</v>
       </c>
       <c r="S174" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>MIS re-refinement: Structure Rule 1 — tail 'Security' is not an action-as-noun; rewrite to end in an action.</t>
         </is>
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>keep:0, "Ad‑Hoc Network Protection/Ad-Hoc Network Protection":2, "Ad‑Hoc Network Security Assessment":1</t>
+          <t>keep:1, "Ad‑Hoc Network Safeguarding":1, "Ad‑Hoc Network Security Implementation":1</t>
         </is>
       </c>
       <c r="V174" t="inlineStr">
@@ -23057,7 +23101,7 @@
         </is>
       </c>
       <c r="Y174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z174" t="b">
         <v>0</v>
@@ -23068,9 +23112,13 @@
       </c>
       <c r="AC174" t="inlineStr"/>
       <c r="AD174" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE174" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>Structure Rule 1 — tail 'Security' is not an action-as-noun; rewrite to end in an action.</t>
+        </is>
+      </c>
       <c r="AF174" t="b">
         <v>0</v>
       </c>
@@ -23143,7 +23191,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>RADIUS; AAA; LDAP; authentication server; configuration</t>
+          <t>authentication server; configuration; RADIUS; AAA; LDAP</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -23161,12 +23209,12 @@
         <v>0</v>
       </c>
       <c r="S175" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr">
         <is>
-          <t>keep:2, "Authentication Server Configuration":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V175" t="inlineStr">
@@ -23243,7 +23291,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Contains career development activities within curricula to enhance student professional readiness.</t>
+          <t>Contains career development learning and professional engagement opportunities within curricula to enhance student professional readiness.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -23287,12 +23335,12 @@
         <v>0</v>
       </c>
       <c r="S176" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr">
         <is>
-          <t>keep:1, "Professional Development Engagement":1, "Career Development Planning":1</t>
+          <t>keep:1, "Professional Development Opportunity Identification":1, "Professional Development Facilitation":1</t>
         </is>
       </c>
       <c r="V176" t="inlineStr">
@@ -23369,7 +23417,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Secure routing protocols protect network traffic and ensure data integrity.</t>
+          <t>Secure routing protocols to protect network traffic and ensure data integrity.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -23410,19 +23458,15 @@
         </is>
       </c>
       <c r="R177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S177" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.925</v>
+      </c>
+      <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr">
         <is>
-          <t>keep:0, "Secure Routing Protocol Implementation":3</t>
+          <t>keep:2, "Secure Routing Protocol Deployment":1</t>
         </is>
       </c>
       <c r="V177" t="inlineStr">
@@ -23499,7 +23543,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Assesses and evaluates security risk levels across hybrid environments.</t>
+          <t>Assesses and evaluates security risk levels across hybrid environments, evaluating threats for mitigation.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -23624,12 +23668,12 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Wireless CIA Principles</t>
+          <t>Wireless CIA Principle Identification</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Applies wireless security concepts by evaluating confidentiality, integrity, and availability in network designs.</t>
+          <t>Covers confidentiality, integrity, and availability in wireless network designs.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -23655,7 +23699,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>information security; confidentiality; integrity; availability; principles</t>
+          <t>information security; confidentiality; integrity; availability; principle</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -23670,15 +23714,19 @@
         </is>
       </c>
       <c r="R179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S179" t="n">
-        <v>0</v>
-      </c>
-      <c r="T179" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>keep:0, "Wireless CIA Evaluation":1, "wireless CIA principle":1, "Wireless CIA Assessment":1</t>
+          <t>keep:0, "Wireless CIA Principle Identification":2, "Wireless CIA Principle Implementation":1</t>
         </is>
       </c>
       <c r="V179" t="inlineStr">
@@ -23687,7 +23735,7 @@
         </is>
       </c>
       <c r="W179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X179" t="inlineStr">
         <is>
@@ -23755,7 +23803,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Applies hybrid testing tools and mitigation techniques to resolve wireless signal impairments.</t>
+          <t>Applies hybrid testing tools and mitigation techniques to address wireless signal impairments.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -23781,7 +23829,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>RF interference mitigation; signal attenuation analysis; wireless troubleshooting; antenna alignment; network diagnostics</t>
+          <t>RF interference mitigation; signal attenuation analysis; antenna alignment; network diagnostics; wireless troubleshooting</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -23880,7 +23928,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Wireless Network Security Design</t>
+          <t>Wireless Security Architecture Application</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -23911,7 +23959,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>WLAN security architecture; encryption protocols (WPA3; TLS); network access control (NAC); enterprise and IoT wireless segmentation; wireless network design</t>
+          <t>WLAN security architecture; encryption protocols (WPA3; TLS); network access control (NAC); enterprise and IoT wireless segmentation; application</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -23926,15 +23974,19 @@
         </is>
       </c>
       <c r="R181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S181" t="n">
-        <v>0</v>
-      </c>
-      <c r="T181" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>keep:0, "Wireless Security Architecture Application":1, "Wireless Network Security Configuration":1, "Wireless Network Security Implementation":1</t>
+          <t>keep:0, "Wireless Security Architecture Application/Wireless Network Security Application":3</t>
         </is>
       </c>
       <c r="V181" t="inlineStr">
@@ -24006,7 +24058,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Wireless Security Protocol Understanding</t>
+          <t>Wireless Security Protocol Familiarisation</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -24037,7 +24089,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>WEP; WPA; RADIUS; WLAN security; wireless security protocol</t>
+          <t>WEP; WPA; RADIUS; wireless security protocol; WLAN security</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -24064,7 +24116,7 @@
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>keep:0, "Wireless Security Protocol Understanding":2, "Wireless Security Protocol Review":1</t>
+          <t>keep:0, "Wireless Security Protocol Familiarisation":2, "Wireless Security Protocol Understanding":1</t>
         </is>
       </c>
       <c r="V182" t="inlineStr">
@@ -24084,13 +24136,9 @@
         <v>1</v>
       </c>
       <c r="Z182" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA182" t="inlineStr">
-        <is>
-          <t>Authentication Server Configuration (LLM verified, sim=0.72)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA182" t="inlineStr"/>
       <c r="AB182" t="b">
         <v>0</v>
       </c>
@@ -24140,12 +24188,12 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Wireless Security Risk Assessment</t>
+          <t>Wireless Security Assessment Reporting</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Creates wireless risk assessment reports in hybrid environments, reporting findings in formal reports.</t>
+          <t>Creates wireless risk assessment reports in hybrid environments, reporting findings on threats.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -24171,7 +24219,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>wireless networks; risk assessment; threat modeling; vulnerability analysis; aircrack-ng</t>
+          <t>wireless networks; risk assessment; threat modeling; vulnerability analysis; assessment reports</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -24186,15 +24234,19 @@
         </is>
       </c>
       <c r="R183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S183" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="T183" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Wireless Security Assessment Reporting/Wireless Risk Assessment Reporting":2, "Wireless Security Risk Assessment":1</t>
         </is>
       </c>
       <c r="V183" t="inlineStr">
@@ -24211,7 +24263,7 @@
         </is>
       </c>
       <c r="Y183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z183" t="b">
         <v>0</v>
@@ -24297,7 +24349,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>RF propagation; multipath fading; interference mitigation; spectrum management; wireless signal impairment</t>
+          <t>RF propagation; multipath fading; wireless signal; signal impairment; wireless</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -24397,7 +24449,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Assesses wireless vulnerability in hybrid network environments to evaluate security risks.</t>
+          <t>Assesses and evaluates security risks in wireless systems within hybrid network environments.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -24446,7 +24498,7 @@
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr">
         <is>
-          <t>keep:2, "Wireless Security Risk Assessment":1</t>
+          <t>keep:2, "Wireless Vulnerability Assessment":1</t>
         </is>
       </c>
       <c r="V185" t="inlineStr">
@@ -24518,12 +24570,12 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Blockchain Fundamentals Comprehension</t>
+          <t>Blockchain Fundamentals Learning</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Introduces core blockchain concepts and processes to peers in coursework.</t>
+          <t>Introduces core blockchain concepts and processes to peers.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -24549,7 +24601,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>distributed ledger; cryptography; consensus algorithms; smart contracts; blockchain</t>
+          <t>distributed ledger; consensus algorithms; smart contracts; decentralized applications; blockchain fundamentals</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -24576,7 +24628,7 @@
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>keep:0, "Blockchain Fundamentals Comprehension":2, "Blockchain Fundamentals Understanding":1</t>
+          <t>keep:0, "Blockchain Fundamentals Learning":2, "Blockchain Fundamentals Study":1</t>
         </is>
       </c>
       <c r="V186" t="inlineStr">
@@ -24604,7 +24656,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>vague skill from course description — "Blockchain Fundamentals Comprehension" uses non-assessable term: {'fundamentals'}</t>
+          <t>vague skill from course description — "Blockchain Fundamentals Learning" uses non-assessable term: {'fundamentals'}</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -24657,7 +24709,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Analyses blockchain use cases and underlying components for applicability in hybrid projects.</t>
+          <t>Analyzes blockchain use cases and underlying components for applicability in hybrid projects.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -24683,7 +24735,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>smart contracts; consensus mechanisms; decentralized applications; distributed ledger technology; usecase</t>
+          <t>smart contracts; consensus mechanisms; decentralized applications; distributed ledger technology; usecase analysis</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -24840,7 +24892,7 @@
       <c r="T188" t="inlineStr"/>
       <c r="U188" t="inlineStr">
         <is>
-          <t>keep:2, "Business Recommendation Development":1</t>
+          <t>keep:2, "Blockchain Recommendation Development":1</t>
         </is>
       </c>
       <c r="V188" t="inlineStr">
@@ -24912,7 +24964,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Commercial-legal Viability Assessment</t>
+          <t>Commercial Legal Environment Assessment</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -24943,7 +24995,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>commercial viability; market analysis; regulatory compliance; crypto business models; feasibility study</t>
+          <t>market analysis; regulatory compliance; crypto business models; commercial environment; legal environment</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -24965,12 +25017,12 @@
       </c>
       <c r="T189" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t>keep:0, "Commercial-Legal Viability Assessment/Commercial Viability Assessment":2, "Commercial Legal Environment Assessment":1</t>
+          <t>keep:0, "Commercial Legal Environment Assessment/Commercial Legal Assessment":3</t>
         </is>
       </c>
       <c r="V189" t="inlineStr">
@@ -24994,7 +25046,7 @@
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>Commercial Legal Environment Assessment</t>
+          <t>Legal Environment Analysis</t>
         </is>
       </c>
       <c r="AB189" t="b">
@@ -25051,7 +25103,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Analyzes cryptocurrency viability by analysing blockchain components and use cases in hybrid environments.</t>
+          <t>Analyses cryptocurrency viability by analysing blockchain components and use cases in hybrid environments.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -25104,7 +25156,7 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>keep:0, "Cryptocurrency Analysis/Cryptocurrency Usecase Analysis":3</t>
+          <t>keep:0, "Cryptocurrency Usecase Analysis/Cryptocurrency Analysis":3</t>
         </is>
       </c>
       <c r="V190" t="inlineStr">
@@ -25128,7 +25180,7 @@
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>Cryptocurrency Analysis</t>
+          <t>Business Recommendation Development (LLM verified, sim=0.74)</t>
         </is>
       </c>
       <c r="AB190" t="b">
@@ -25180,12 +25232,12 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cryptocurrency Analysis</t>
+          <t>Cryptocurrency Transaction Analysis</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Uses cryptocurrency market trends to support peer-to-peer financial transactions without banks.</t>
+          <t>Cryptocurrency market trends for peer-to-peer financial transactions without banks.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -25211,7 +25263,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>blockchain; digital assets; crypto trading; cryptocurrency; decentralized finance</t>
+          <t>blockchain; digital assets; crypto trading; cryptocurrency; transaction</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -25233,12 +25285,12 @@
       </c>
       <c r="T191" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>keep:0, "Cryptocurrency Analysis/Cryptocurrency Transaction Analysis/Cryptocurrency Usecase Analysis":3</t>
+          <t>keep:0, "Cryptocurrency Transaction Analysis":2, "Cryptocurrency Evaluation":1</t>
         </is>
       </c>
       <c r="V191" t="inlineStr">
@@ -25310,7 +25362,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Transaction Development</t>
+          <t>Digital Transaction Design</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -25341,7 +25393,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>blockchain; distributed ledger; smart contracts; decentralized finance; transaction</t>
+          <t>blockchain; distributed ledger; cryptography; digital transaction; transaction design</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -25356,19 +25408,15 @@
         </is>
       </c>
       <c r="R192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S192" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T192" t="inlineStr"/>
       <c r="U192" t="inlineStr">
         <is>
-          <t>keep:0, "Transaction Development/Digital Transaction Development":2, "Digital Transaction Securing":1</t>
+          <t>keep:1, "Digital Transaction Securing":1, "Blockchain Transaction Design":1</t>
         </is>
       </c>
       <c r="V192" t="inlineStr">
@@ -25498,7 +25546,7 @@
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>keep:0, "Ledger Security Measures Explanation/Distributed Ledger Security Explanation":3</t>
+          <t>keep:0, "Distributed Ledger Security Explanation":3</t>
         </is>
       </c>
       <c r="V193" t="inlineStr">
@@ -25574,12 +25622,12 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Commercial Legal Environment Assessment</t>
+          <t>Legal Environment Analysis</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Assesses commercial and legal landscapes for crypto startups, ensuring compliance and market strategy.</t>
+          <t>Assesses commercial and legal landscapes for crypto startups, ensuring compliance and informing market strategy.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -25605,7 +25653,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>cryptocurrency regulation; commercial law; blockchain legal frameworks; AML/KYC requirements; business success</t>
+          <t>cryptocurrency regulation; fintech compliance; commercial law; blockchain legal frameworks; AML/KYC requirements</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -25620,19 +25668,15 @@
         </is>
       </c>
       <c r="R194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S194" t="n">
         <v>0.9</v>
       </c>
-      <c r="T194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+      <c r="T194" t="inlineStr"/>
       <c r="U194" t="inlineStr">
         <is>
-          <t>keep:0, "Commercial Legal Environment Assessment":3</t>
+          <t>keep:1, "Commercial Legal Environment Assessment":1, "Commercial-Legal Environment Assessment":1</t>
         </is>
       </c>
       <c r="V194" t="inlineStr">
@@ -25649,7 +25693,7 @@
         </is>
       </c>
       <c r="Y194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z194" t="b">
         <v>1</v>
@@ -25739,7 +25783,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>cryptocurrency; AML/KYC; legal environment analysis; blockchain compliance; commercial environment</t>
+          <t>cryptocurrency; fintech regulation; legal environment analysis; blockchain compliance; commercial environment</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -25761,12 +25805,12 @@
       </c>
       <c r="T195" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>keep:0, "Commercial Legal Environment Assessment":3</t>
+          <t>keep:1, "Commercial Legal Environment Assessment":2</t>
         </is>
       </c>
       <c r="V195" t="inlineStr">
@@ -25896,7 +25940,7 @@
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>keep:0, "Security Measures Explanation/Ledger Security Measures Explanation":3</t>
+          <t>keep:0, "Security Measures Explanation":3</t>
         </is>
       </c>
       <c r="V196" t="inlineStr">
@@ -26018,19 +26062,15 @@
         </is>
       </c>
       <c r="R197" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S197" t="n">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="T197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr">
         <is>
-          <t>keep:0, "Distributed-Ledger Security Measures Explanation/Security Measures Explanation":3</t>
+          <t>keep:2, "Security Measures Explanation":1</t>
         </is>
       </c>
       <c r="V197" t="inlineStr">
@@ -26102,7 +26142,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Smart Contract Assessment</t>
+          <t>Smart Contract Analysis</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -26160,7 +26200,7 @@
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>keep:0, "Smart Contract Assessment":2, "Blockchain Transaction Assessment":1</t>
+          <t>keep:0, "Smart Contract Analysis":2, "Smart Contract Application":1</t>
         </is>
       </c>
       <c r="V198" t="inlineStr">
@@ -26232,7 +26272,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Recommendation Development</t>
+          <t>Business Recommendation Development</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -26285,12 +26325,12 @@
       </c>
       <c r="T199" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>keep:0, "Recommendation Development":2, "Recommendation Communication":1</t>
+          <t>keep:0, "Business Recommendation Development":3</t>
         </is>
       </c>
       <c r="V199" t="inlineStr">
@@ -26366,7 +26406,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Recommendation Planning</t>
+          <t>Blockchain Recommendation Development</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -26424,7 +26464,7 @@
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>keep:0, "Recommendation Planning":2, "Usage Recommendation Development":1</t>
+          <t>keep:0, "Blockchain Recommendation Development/Business Recommendation Development":2, "Blockchain Usage Recommendation":1</t>
         </is>
       </c>
       <c r="V200" t="inlineStr">
@@ -26550,12 +26590,12 @@
         <v>0</v>
       </c>
       <c r="S201" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T201" t="inlineStr"/>
       <c r="U201" t="inlineStr">
         <is>
-          <t>keep:2, "Distance Vector Routing Implementation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V201" t="inlineStr">
@@ -26575,9 +26615,13 @@
         <v>1</v>
       </c>
       <c r="Z201" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA201" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>Link State Implementation</t>
+        </is>
+      </c>
       <c r="AB201" t="b">
         <v>0</v>
       </c>
@@ -26659,7 +26703,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>configuration; routing protocols; OSPF; BGP; dynamic routing</t>
+          <t>routing protocols; OSPF; BGP; dynamic routing; router configuration</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -26677,12 +26721,12 @@
         <v>0</v>
       </c>
       <c r="S202" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T202" t="inlineStr"/>
       <c r="U202" t="inlineStr">
         <is>
-          <t>keep:2, "Dynamic Routing Configuration":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V202" t="inlineStr">
@@ -26702,9 +26746,13 @@
         <v>1</v>
       </c>
       <c r="Z202" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA202" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>Static Routing Configuration</t>
+        </is>
+      </c>
       <c r="AB202" t="b">
         <v>0</v>
       </c>
@@ -26755,7 +26803,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Ipng Addressing Scheme Evaluation</t>
+          <t>Ipng Addressing Evaluation</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -26786,7 +26834,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>IPv6; subnetting; address allocation; network architecture; ipng addressing scheme</t>
+          <t>ipng; addressing; IPv6; subnetting; address allocation</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -26808,12 +26856,12 @@
       </c>
       <c r="T203" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>keep:0, "IPng Addressing Scheme Evaluation/IPng Addressing Evaluation":2, "IPng Addressing Scheme Development":1</t>
+          <t>keep:0, "IPng Addressing Evaluation/IPng Addressing Scheme Evaluation":3</t>
         </is>
       </c>
       <c r="V203" t="inlineStr">
@@ -26890,7 +26938,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Link State Routing Implementation</t>
+          <t>Link State Implementation</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -26936,19 +26984,15 @@
         </is>
       </c>
       <c r="R204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S204" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr">
         <is>
-          <t>keep:1, "Link State Routing Implementation":2</t>
+          <t>keep:2, "Link State Routing Implementation":1</t>
         </is>
       </c>
       <c r="V204" t="inlineStr">
@@ -26968,13 +27012,9 @@
         <v>0</v>
       </c>
       <c r="Z204" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>Distance Vector Implementation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA204" t="inlineStr"/>
       <c r="AB204" t="b">
         <v>0</v>
       </c>
@@ -27056,7 +27096,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>network stack; protocol integration; socket programming; cross‑protocol communication; multiprotocol network</t>
+          <t>network stack; protocol integration; embedded networking; cross‑protocol communication; multiprotocol network</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -27152,7 +27192,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Protocol Performance Evaluation</t>
+          <t>Routing Protocol Performance Evaluation</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -27183,7 +27223,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>protocol performance evaluation; latency and throughput analysis; network simulation; network environments; network diagnostics</t>
+          <t>protocol performance evaluation; latency and throughput analysis; network simulation; routing protocols; network diagnostics</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -27205,12 +27245,12 @@
       </c>
       <c r="T206" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>keep:0, "Protocol Performance Evaluation/Routing Protocol Performance Evaluation/Network Protocol Performance Evaluation":3</t>
+          <t>keep:0, "Routing Protocol Performance Evaluation/Protocol Performance Evaluation":2, "Network Environment Testing":1</t>
         </is>
       </c>
       <c r="V206" t="inlineStr">
@@ -27467,12 +27507,12 @@
       </c>
       <c r="T208" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>keep:0, "Routing Protocol Assessment":3</t>
+          <t>keep:0, "Routing Protocol Assessment":2, "Routing Protocol Analysis":1</t>
         </is>
       </c>
       <c r="V208" t="inlineStr">
@@ -27580,7 +27620,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>routing protocols; protocol evaluation; OSPF; BGP; packet tracing</t>
+          <t>network performance analysis; protocol evaluation; OSPF; BGP; routing protocols</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -27598,12 +27638,12 @@
         <v>0</v>
       </c>
       <c r="S209" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T209" t="inlineStr"/>
       <c r="U209" t="inlineStr">
         <is>
-          <t>keep:2, "Routing Protocol Assessment":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V209" t="inlineStr">
@@ -27707,7 +27747,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>network simulation; performance metrics; routing protocols; throughput analysis; QoS evaluation</t>
+          <t>network simulation; performance metrics; routing protocols; protocol performance; throughput analysis</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -27725,12 +27765,12 @@
         <v>0</v>
       </c>
       <c r="S210" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T210" t="inlineStr"/>
       <c r="U210" t="inlineStr">
         <is>
-          <t>keep:2, "Routing Protocol Performance Evaluation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V210" t="inlineStr">
@@ -27808,7 +27848,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Constructs and interprets routing tables to support optimal network paths and troubleshoot connectivity.</t>
+          <t>Constructs and interprets routing tables for optimal network paths and troubleshooting connectivity.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -27834,7 +27874,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>network engineering; routing protocols; IP addressing; packet forwarding; routing table</t>
+          <t>routing table; network engineering; routing protocols; IP addressing; packet forwarding</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -27852,12 +27892,12 @@
         <v>0</v>
       </c>
       <c r="S211" t="n">
-        <v>0.7749999999999999</v>
+        <v>0.925</v>
       </c>
       <c r="T211" t="inlineStr"/>
       <c r="U211" t="inlineStr">
         <is>
-          <t>keep:2, "Routing Table Management":1</t>
+          <t>keep:2, "Routing Table Development":1</t>
         </is>
       </c>
       <c r="V211" t="inlineStr">
@@ -27939,7 +27979,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Constructs and interprets routing tables to troubleshoot connectivity issues.</t>
+          <t>Interprets routing tables to troubleshoot connectivity issues.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -27965,7 +28005,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>networking; IP routing; Cisco IOS; routing table; interpretation</t>
+          <t>networking; IP routing; BGP; OSPF; routing tables</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -27980,19 +28020,15 @@
         </is>
       </c>
       <c r="R212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S212" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T212" t="inlineStr"/>
       <c r="U212" t="inlineStr">
         <is>
-          <t>keep:1, "Routing Table Interpretation":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V212" t="inlineStr">
@@ -28139,13 +28175,9 @@
         <v>1</v>
       </c>
       <c r="Z213" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA213" t="inlineStr">
-        <is>
-          <t>Dynamic Routing Configuration</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA213" t="inlineStr"/>
       <c r="AB213" t="b">
         <v>0</v>
       </c>
@@ -28201,7 +28233,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Describes and evaluates IPng addressing and subnetting designs, evaluating limitations in theoretical models.</t>
+          <t>Describes and evaluates IPng addressing and subnetting, noting limitations in theoretical models.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -28250,7 +28282,7 @@
       <c r="T214" t="inlineStr"/>
       <c r="U214" t="inlineStr">
         <is>
-          <t>keep:2, "IPng Addressing Evaluation":1</t>
+          <t>keep:1, "Subnetting Evaluation":1, "IPng Addressing Evaluation":1</t>
         </is>
       </c>
       <c r="V214" t="inlineStr">
@@ -28498,16 +28530,16 @@
         <v>1</v>
       </c>
       <c r="S216" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>MIS re-refinement: Structure Rule 1 — tail 'Concepts' is not an action-as-noun; rewrite to end in an action.</t>
         </is>
       </c>
       <c r="U216" t="inlineStr">
         <is>
-          <t>keep:0, "Forensic Concept Evaluation":2, "Forensic Concept Appraisal":1</t>
+          <t>keep:0, "Forensic Concepts Critical Assessment":1, "Forensic Concept Evaluation":1, "Forensic Concept Assessment":1</t>
         </is>
       </c>
       <c r="V216" t="inlineStr">
@@ -28535,9 +28567,13 @@
       </c>
       <c r="AC216" t="inlineStr"/>
       <c r="AD216" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE216" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>Structure Rule 1 — tail 'Concepts' is not an action-as-noun; rewrite to end in an action.</t>
+        </is>
+      </c>
       <c r="AF216" t="b">
         <v>0</v>
       </c>
@@ -28628,12 +28664,12 @@
         <v>0</v>
       </c>
       <c r="S217" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T217" t="inlineStr"/>
       <c r="U217" t="inlineStr">
         <is>
-          <t>keep:2, "Digital Evidence Analysis":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V217" t="inlineStr">
@@ -28705,7 +28741,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Digital Forensic Process Analysis</t>
+          <t>Digital Forensic Process Investigation</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -28736,7 +28772,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>digital forensic; evidence acquisition; chain of custody; forensic tools; memory analysis</t>
+          <t>digital investigation; evidence acquisition; chain of custody; forensic tools; memory analysis</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -28754,7 +28790,7 @@
         <v>1</v>
       </c>
       <c r="S218" t="n">
-        <v>0.925</v>
+        <v>0.9</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -28763,7 +28799,7 @@
       </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>keep:0, "Digital Forensic Process Analysis":2, "Digital Forensic Process Investigation":1</t>
+          <t>keep:1, "Digital Forensic Process Investigation":2</t>
         </is>
       </c>
       <c r="V218" t="inlineStr">
@@ -28835,12 +28871,12 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Forensic Evidence Documentation</t>
+          <t>Forensic Documentation Ethical Summarisation</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Summarises ethical and legal requirements when handling forensic evidence to ensure compliance.</t>
+          <t>Summarizes ethical and legal requirements when documenting forensic evidence to ensure compliance.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -28866,7 +28902,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>forensic ethics; chain of custody; evidence documentation; legal compliance; criminal justice standards</t>
+          <t>forensic ethics; chain of custody; evidence documentation; legal compliance; ethical considerations</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -28893,7 +28929,7 @@
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>keep:0, "Forensic Evidence Documentation":2, "Forensic Documentation Summarisation":1</t>
+          <t>keep:0, "Forensic Documentation Ethical Summarisation/Forensic Documentation Ethics Summarisation":2, "Forensic Documentation Ethics Assessment":1</t>
         </is>
       </c>
       <c r="V219" t="inlineStr">
@@ -28902,7 +28938,7 @@
         </is>
       </c>
       <c r="W219" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X219" t="inlineStr">
         <is>
@@ -28910,14 +28946,14 @@
         </is>
       </c>
       <c r="Y219" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z219" t="b">
         <v>1</v>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>Forensic Evidence Documentation</t>
+          <t>Forensic Evidence Documentation Summarisation</t>
         </is>
       </c>
       <c r="AB219" t="b">
@@ -28974,7 +29010,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Uncovers hidden data and confirms integrity of digital evidence for investigations.</t>
+          <t>Digital evidence is uncovered, hidden data is revealed and integrity is confirmed for investigations.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -29000,7 +29036,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>digital forensics; chain of custody; evidence handling; collection; validation</t>
+          <t>digital forensics; data integrity; chain of custody; evidence collection; validation</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -29095,12 +29131,12 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Forensic Evidence Documentation</t>
+          <t>Forensic Evidence Documentation Summarisation</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Summarises ethical and legal guidelines for documentation of forensic evidence in hybrid investigations.</t>
+          <t>Summarises ethical and legal guidelines for forensic evidence in hybrid investigations.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -29126,7 +29162,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>chain of custody; ethical standards; crime scene documentation; forensic reporting; forensic evidence</t>
+          <t>chain of custody; legal compliance; ethical standards; evidence; summarisation</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -29141,15 +29177,19 @@
         </is>
       </c>
       <c r="R221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S221" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T221" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>keep:2, "Forensic Evidence Documentation":1</t>
+          <t>keep:1, "Forensic Evidence Documentation Summarisation":2</t>
         </is>
       </c>
       <c r="V221" t="inlineStr">
@@ -29169,9 +29209,13 @@
         <v>1</v>
       </c>
       <c r="Z221" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA221" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>Forensic Evidence Documentation</t>
+        </is>
+      </c>
       <c r="AB221" t="b">
         <v>0</v>
       </c>
@@ -29221,7 +29265,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Forensic Investigative Procedures</t>
+          <t>Investigative Procedure Application</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -29252,7 +29296,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>digital forensics; evidence acquisition; investigative procedures; forensic analysis tools; chain of custody</t>
+          <t>digital forensics; evidence acquisition; forensic analysis tools; chain of custody; investigative procedures</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -29267,15 +29311,19 @@
         </is>
       </c>
       <c r="R222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S222" t="n">
-        <v>0</v>
-      </c>
-      <c r="T222" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>keep:0, "Forensic Investigative Procedure Application":1, "Forensic Investigation Application":1, "Forensic Investigation Execution":1</t>
+          <t>keep:0, "Investigative Procedure Application":2, "Forensic Investigation Application":1</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
@@ -29378,7 +29426,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>forensic evidence handling; chain of custody; regulatory standards; admissibility requirements; forensic evidence documentation</t>
+          <t>forensic evidence handling; chain of custody; regulatory standards; admissibility requirements; legal considerations</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -29425,13 +29473,9 @@
         <v>1</v>
       </c>
       <c r="Z223" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA223" t="inlineStr">
-        <is>
-          <t>Forensic Evidence Documentation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA223" t="inlineStr"/>
       <c r="AB223" t="b">
         <v>0</v>
       </c>
@@ -29481,12 +29525,12 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Network Traffic Analysis</t>
+          <t>Traffic Analysis</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Performs network traffic analysis to extract forensic evidence from digital environments.</t>
+          <t>Analyses network traffic to extract forensic evidence from digital environments.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -29527,15 +29571,19 @@
         </is>
       </c>
       <c r="R224" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S224" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T224" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>keep:2, "Network Traffic Examination":1</t>
+          <t>keep:0, "Traffic Analysis":3</t>
         </is>
       </c>
       <c r="V224" t="inlineStr">
@@ -29638,7 +29686,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>digital forensics; forensic software; evidence collection; tool implementation; application</t>
+          <t>digital forensics; forensic software; evidence collection; case study analysis; tool implementation</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -29660,12 +29708,12 @@
       </c>
       <c r="T225" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>keep:1, "Forensic Tool Application":2</t>
+          <t>keep:0, "Forensic Tool Application":3</t>
         </is>
       </c>
       <c r="V225" t="inlineStr">
@@ -29682,7 +29730,7 @@
         </is>
       </c>
       <c r="Y225" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z225" t="b">
         <v>0</v>
@@ -29768,7 +29816,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>report writing; data visualization; client communication; business analysis; presentation tools</t>
+          <t>report writing; data visualization; client communication; client reports; presentation tools</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -29783,15 +29831,19 @@
         </is>
       </c>
       <c r="R226" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S226" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T226" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>keep:2, "Client Report Development":1</t>
+          <t>keep:1, "Client Report Development":2</t>
         </is>
       </c>
       <c r="V226" t="inlineStr">
@@ -29808,12 +29860,16 @@
         </is>
       </c>
       <c r="Y226" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z226" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA226" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>Findings Communication (LLM verified, sim=0.68)</t>
+        </is>
+      </c>
       <c r="AB226" t="b">
         <v>0</v>
       </c>
@@ -29863,12 +29919,12 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Ethical Legal Compliance</t>
+          <t>Ethical Legal Obligation Assessment</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Ensures adherence to ethical standards and legal obligations in academic research and policy development.</t>
+          <t>Adherence to ethical standards and legal obligations in academic research and policy development.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -29894,7 +29950,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>regulatory; risk management; legal frameworks; ethical; compliance</t>
+          <t>ethical; obligation; regulatory; governance; legal frameworks</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
@@ -29909,15 +29965,19 @@
         </is>
       </c>
       <c r="R227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S227" t="n">
         <v>0.95</v>
       </c>
-      <c r="T227" t="inlineStr"/>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>MIS re-refinement: Structure Rule 4 — tail 'Compliance' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>keep:1, "Penetration Testing Compliance":1, "Ethical Legal Obligations Assessment":1</t>
+          <t>keep:2, "Ethical Legal Obligation Compliance":1</t>
         </is>
       </c>
       <c r="V227" t="inlineStr">
@@ -29926,7 +29986,7 @@
         </is>
       </c>
       <c r="W227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X227" t="inlineStr">
         <is>
@@ -29945,9 +30005,13 @@
       </c>
       <c r="AC227" t="inlineStr"/>
       <c r="AD227" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE227" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>Structure Rule 4 — tail 'Compliance' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="AF227" t="b">
         <v>0</v>
       </c>
@@ -29989,12 +30053,12 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Security Vulnerability Exploitation</t>
+          <t>Vulnerability Exploitation</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Exploits common security vulnerabilities to identify them in systems.</t>
+          <t>Identifies and exploits common security vulnerabilities in systems.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -30020,7 +30084,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>penetration testing; vulnerability exploitation; buffer overflow; Metasploit; common security vulnerabilities</t>
+          <t>penetration testing; vulnerability exploitation; buffer overflow; Metasploit; security vulnerabilities</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -30047,7 +30111,7 @@
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>keep:0, "Security Vulnerability Exploitation/Vulnerability Exploitation":3</t>
+          <t>keep:0, "Vulnerability Exploitation":3</t>
         </is>
       </c>
       <c r="V228" t="inlineStr">
@@ -30128,7 +30192,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Interprets results from standard penetration testing tools and tests identified vulnerabilities.</t>
+          <t>Interprets outputs from standard penetration testing tools and tests for vulnerabilities.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -30154,7 +30218,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>vulnerability assessment; exploit analysis; Metasploit; Nmap; penetration testing results</t>
+          <t>vulnerability assessment; Metasploit; Nmap; penetration testing; test results</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -30177,7 +30241,7 @@
       <c r="T229" t="inlineStr"/>
       <c r="U229" t="inlineStr">
         <is>
-          <t>keep:2, "Penetration Test Result Interpretation":1</t>
+          <t>keep:2, "Penetration Test Results Interpretation":1</t>
         </is>
       </c>
       <c r="V229" t="inlineStr">
@@ -30254,7 +30318,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Ensures penetration tests comply with ethical standards and legal regulations by complying with obligations before execution.</t>
+          <t>Ensures penetration tests comply with ethical standards and legal regulations by considering obligations before execution.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -30280,7 +30344,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>ethical hacking; cybersecurity compliance; legal regulations; information security law; ethical obligations</t>
+          <t>ethical hacking; legal regulations; information security law; legal obligations; cybersecurity compliance</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -30302,12 +30366,12 @@
       </c>
       <c r="T230" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>keep:0, "Penetration Testing Legal Compliance/Legal Compliance":3</t>
+          <t>keep:0, "Penetration Testing Legal Compliance/Penetration Testing Ethical Compliance":2, "Ethical Legal Compliance":1</t>
         </is>
       </c>
       <c r="V230" t="inlineStr">
@@ -30331,7 +30395,7 @@
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>Ethical Legal Compliance</t>
+          <t>Ethical Legal Obligation Assessment</t>
         </is>
       </c>
       <c r="AB230" t="b">
@@ -30339,9 +30403,13 @@
       </c>
       <c r="AC230" t="inlineStr"/>
       <c r="AD230" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE230" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>Structure Rule 4 — tail 'Compliance' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="AF230" t="b">
         <v>0</v>
       </c>
@@ -30383,7 +30451,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Penetration Testing Methodology Implementation</t>
+          <t>Penetration Testing Methodology Application</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -30414,7 +30482,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>ethical hacking; vulnerability assessment; red team operations; penetration methodology; penetration testing</t>
+          <t>ethical hacking; vulnerability assessment; red team operations; penetration testing; methodology</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -30436,12 +30504,12 @@
       </c>
       <c r="T231" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>keep:0, "Penetration Testing Methodology Implementation/Penetration Testing Implementation":2, "Penetration Testing Methodology Application":1</t>
+          <t>keep:0, "Penetration Testing Methodology Application":3</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
@@ -30465,7 +30533,7 @@
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>Penetration Testing Tool Utilisation (LLM verified, sim=0.64)</t>
+          <t>Penetration Testing Principles Understanding (LLM verified, sim=0.68)</t>
         </is>
       </c>
       <c r="AB231" t="b">
@@ -30517,7 +30585,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Penetration Testing Principles Comprehension</t>
+          <t>Penetration Testing Principles Understanding</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -30548,7 +30616,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>ethical hacking; vulnerability assessment; exploit development; network security; penetration testing principles</t>
+          <t>ethical hacking; vulnerability assessment; exploit development; penetration testing; OWASP methodology</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -30575,7 +30643,7 @@
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>keep:0, "Penetration Testing Principles Comprehension/Penetration Testing Comprehension":2, "Penetration Testing Principle Review":1</t>
+          <t>keep:0, "Penetration Testing Principles Understanding/Penetration Testing Principle Understanding":2, "Penetration Testing Principles Review":1</t>
         </is>
       </c>
       <c r="V232" t="inlineStr">
@@ -30599,9 +30667,13 @@
       </c>
       <c r="AA232" t="inlineStr"/>
       <c r="AB232" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC232" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>vague skill from course description — "Penetration Testing Principles Understanding" uses non-assessable term: {'understanding'}</t>
+        </is>
+      </c>
       <c r="AD232" t="b">
         <v>0</v>
       </c>
@@ -30652,7 +30724,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Tests penetration tools to assess vulnerabilities.</t>
+          <t>Tests penetration testing tools to assess vulnerabilities.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -30678,7 +30750,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>ethical hacking; Metasploit; Nmap; Kali Linux; penetration testing</t>
+          <t>penetration testing; vulnerability assessment; Metasploit; Nmap; Kali Linux</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -30705,7 +30777,7 @@
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>keep:2, "Penetration Testing Tool Utilisation":1</t>
+          <t>keep:2, "Penetration Testing Tool Utilization":1</t>
         </is>
       </c>
       <c r="V233" t="inlineStr">
@@ -30835,7 +30907,7 @@
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>keep:0, "Findings Communication/Stakeholder Findings Communication":3</t>
+          <t>keep:0, "Findings Communication":3</t>
         </is>
       </c>
       <c r="V234" t="inlineStr">
@@ -30855,13 +30927,9 @@
         <v>1</v>
       </c>
       <c r="Z234" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA234" t="inlineStr">
-        <is>
-          <t>Client Report Development (LLM verified, sim=0.68)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA234" t="inlineStr"/>
       <c r="AB234" t="b">
         <v>0</v>
       </c>
@@ -30942,7 +31010,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>cybersecurity; risk assessment; security recommendation; access control; compliance governance</t>
+          <t>cybersecurity; risk assessment; NIST framework; access control; recommendation</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -31086,12 +31154,12 @@
         <v>0</v>
       </c>
       <c r="S236" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T236" t="inlineStr"/>
       <c r="U236" t="inlineStr">
         <is>
-          <t>keep:2, "Security Resilience Enhancement":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V236" t="inlineStr">
@@ -31163,7 +31231,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Security Testing Phase Awareness</t>
+          <t>Security Testing Phase Familiarisation</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -31194,7 +31262,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>penetration testing; vulnerability assessment; security testing phases; red team/blue team methodology; security awareness</t>
+          <t>penetration testing; security testing phases; red team/blue team methodology; OWASP testing guide; familiarisation</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
@@ -31209,15 +31277,19 @@
         </is>
       </c>
       <c r="R237" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S237" t="n">
-        <v>0</v>
-      </c>
-      <c r="T237" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U237" t="inlineStr">
         <is>
-          <t>keep:0, "Penetration Testing Phase Review":1, "Penetration Testing Phase Recognition":1, "Security Testing Phase Understanding":1</t>
+          <t>keep:0, "Security Testing Phase Familiarisation":2, "Testing Phase Identification":1</t>
         </is>
       </c>
       <c r="V237" t="inlineStr">
@@ -31241,13 +31313,9 @@
       </c>
       <c r="AA237" t="inlineStr"/>
       <c r="AB237" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>vague skill from course description — "Security Testing Phase Awareness" uses non-assessable term: {'awareness'}</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC237" t="inlineStr"/>
       <c r="AD237" t="b">
         <v>0</v>
       </c>
@@ -31293,7 +31361,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Penetration Testing Value Articulation</t>
+          <t>Security Testing Value Articulation</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -31324,7 +31392,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>penetration testing; vulnerability assessment; cyber risk valuation; ethical hacking; value articulation</t>
+          <t>penetration testing; ethical hacking; cyber risk valuation; vulnerability assessment; value articulation</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
@@ -31339,19 +31407,15 @@
         </is>
       </c>
       <c r="R238" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S238" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T238" t="inlineStr"/>
       <c r="U238" t="inlineStr">
         <is>
-          <t>keep:0, "Penetration Testing Value Articulation":2, "Security Testing Value Recognition":1</t>
+          <t>keep:2, "Penetration Testing Value Articulation":1</t>
         </is>
       </c>
       <c r="V238" t="inlineStr">
@@ -31454,7 +31518,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>penetration testing; vulnerability assessment; ethical hacking; comparison; attack vectors</t>
+          <t>penetration testing; vulnerability assessment; ethical hacking; security concepts; comparison</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
@@ -31476,12 +31540,12 @@
       </c>
       <c r="T239" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>keep:1, "Penetration Testing Concepts Comparison":2</t>
+          <t>keep:0, "Penetration Testing Concepts Comparison":3</t>
         </is>
       </c>
       <c r="V239" t="inlineStr">
@@ -31606,12 +31670,12 @@
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>keep:0, "Vulnerability Exploitation":2, "Vulnerability Identification":1</t>
+          <t>keep:0, "Vulnerability Exploitation":3</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
@@ -31737,7 +31801,7 @@
       <c r="T241" t="inlineStr"/>
       <c r="U241" t="inlineStr">
         <is>
-          <t>keep:1, "Cryptographic Algorithm Implementation":1, "Cloud Cryptography Implementation":1</t>
+          <t>keep:1, "Cloud Cryptographic Implementation":1, "Cloud Cryptographic Application":1</t>
         </is>
       </c>
       <c r="V241" t="inlineStr">
@@ -31887,7 +31951,7 @@
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>Digital Signature Deployment</t>
+          <t>Hash Function Utilisation</t>
         </is>
       </c>
       <c r="AB242" t="b">
@@ -31939,12 +32003,12 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Cybersecurity Innovation Evaluation</t>
+          <t>Cybersecurity Innovation Analysis</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Emerging cybersecurity concepts theoretically for novel protection strategies.</t>
+          <t>Evaluates emerging cybersecurity concepts theoretically to identify novel protection strategies.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -31970,7 +32034,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>threat intelligence; emerging cyber‑defense technologies; AI‑driven threat detection; cybersecurity; innovation</t>
+          <t>threat intelligence; security research; emerging cyber‑defense technologies; AI‑driven threat detection; cybersecurity innovation</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
@@ -31985,19 +32049,15 @@
         </is>
       </c>
       <c r="R243" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S243" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T243" t="inlineStr"/>
       <c r="U243" t="inlineStr">
         <is>
-          <t>keep:0, "Cybersecurity Innovation Evaluation/Cybersecurity Paradigm Evaluation":2, "Cybersecurity Innovation Assessment":1</t>
+          <t>keep:0, "Cybersecurity Innovation":1, "Cybersecurity Innovation Evaluation":1, "Cybersecurity Innovation Assessment":1</t>
         </is>
       </c>
       <c r="V243" t="inlineStr">
@@ -32006,7 +32066,7 @@
         </is>
       </c>
       <c r="W243" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X243" t="inlineStr">
         <is>
@@ -32069,12 +32129,12 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Digital Signature Deployment</t>
+          <t>Cryptographic Algorithm Application</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Applies digital signature solutions using cryptographic algorithms to protect system and network communications.</t>
+          <t>Applies digital signature solutions by integrating cryptographic algorithms to protect system and network communications.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -32100,7 +32160,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>cryptography; public key infrastructure; hash functions; key exchange protocols; digital signatures</t>
+          <t>cryptography; hash functions; key exchange protocols; security protocols; cryptographic algorithm</t>
         </is>
       </c>
       <c r="O244" t="inlineStr">
@@ -32115,15 +32175,19 @@
         </is>
       </c>
       <c r="R244" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S244" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T244" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>keep:2, "Digital Signature Application":1</t>
+          <t>keep:0, "Cryptographic Algorithm Application":2, "Digital Signature Deployment":1</t>
         </is>
       </c>
       <c r="V244" t="inlineStr">
@@ -32147,7 +32211,7 @@
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>Key Exchange Protocol Implementation</t>
+          <t>Cryptographic Algorithm Application</t>
         </is>
       </c>
       <c r="AB244" t="b">
@@ -32199,7 +32263,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Cryptographic Algorithm Implementation</t>
+          <t>Cryptographic Algorithm Application</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -32230,7 +32294,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>cryptography; hash functions; digital signatures; key exchange protocols; algorithm</t>
+          <t>cryptographic algorithm; cryptography; hash functions; digital signatures; key exchange protocols</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
@@ -32252,12 +32316,12 @@
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>keep:0, "Cryptographic Algorithm Implementation":3</t>
+          <t>keep:0, "Cryptographic Algorithm Application/Cryptographic Algorithms Application":2, "Cryptographic Algorithm Implementation":1</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
@@ -32382,12 +32446,12 @@
         <v>0</v>
       </c>
       <c r="S246" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="T246" t="inlineStr"/>
       <c r="U246" t="inlineStr">
         <is>
-          <t>keep:0, "Ethical Legal Considerations Analysis":1, "Ethical-Legal Considerations Analysis":1, "Ethical Legal Consideration Investigation":1</t>
+          <t>keep:1, "Ethical Legal Considerations Analysis":1, "Ethical Legal Considerations Investigation":1</t>
         </is>
       </c>
       <c r="V246" t="inlineStr">
@@ -32490,7 +32554,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>cryptography; hash function; digital signatures; key exchange protocols; encryption methods</t>
+          <t>cryptography; hash function; digital signatures; encryption methods; key exchange protocols</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
@@ -32508,7 +32572,7 @@
         <v>1</v>
       </c>
       <c r="S247" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -32517,7 +32581,7 @@
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>keep:0, "Cryptographic Algorithm Application":1, "Hash Function Application":1, "Hash Function Utilisation":1</t>
+          <t>keep:2, "Hash Function Utilization":1</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
@@ -32541,7 +32605,7 @@
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>Cryptographic Algorithm Application</t>
+          <t>Key Exchange Protocol Implementation</t>
         </is>
       </c>
       <c r="AB247" t="b">
@@ -32624,7 +32688,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>cryptography; key exchange; encryption; digital signatures; protocol</t>
+          <t>cryptography; key exchange; protocol; encryption; digital signatures</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
@@ -32647,7 +32711,7 @@
       <c r="T248" t="inlineStr"/>
       <c r="U248" t="inlineStr">
         <is>
-          <t>keep:2, "Key Exchange Protocol Implementation":1</t>
+          <t>keep:2, "Key Exchange Protocol Application":1</t>
         </is>
       </c>
       <c r="V248" t="inlineStr">
@@ -32719,7 +32783,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Network Vulnerability Analysis</t>
+          <t>Network Security Assessment</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -32750,7 +32814,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>cybersecurity; vulnerability assessment; penetration testing; cloud security; network security</t>
+          <t>cybersecurity; vulnerability assessment; cloud security; intrusion detection; network security</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
@@ -32765,19 +32829,15 @@
         </is>
       </c>
       <c r="R249" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S249" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T249" t="inlineStr"/>
       <c r="U249" t="inlineStr">
         <is>
-          <t>keep:0, "Network Vulnerability Analysis":3</t>
+          <t>keep:1, "Network Vulnerability Assessment":1, "Network Vulnerability Analysis":1</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
@@ -32858,7 +32918,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Analyzes security attacks on system services to assess vulnerabilities.</t>
+          <t>Analyses security attacks on system services to assess vulnerabilities.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -32884,7 +32944,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>cybersecurity; intrusion detection; vulnerability assessment; attack vectors; system services</t>
+          <t>cybersecurity; threat modeling; intrusion detection; vulnerability assessment; attack vectors</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
@@ -32899,19 +32959,15 @@
         </is>
       </c>
       <c r="R250" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S250" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T250" t="inlineStr"/>
       <c r="U250" t="inlineStr">
         <is>
-          <t>keep:1, "Security Attack Analysis":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V250" t="inlineStr">
@@ -32928,7 +32984,7 @@
         </is>
       </c>
       <c r="Y250" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z250" t="b">
         <v>0</v>
@@ -32983,7 +33039,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Vulnerability Assessment</t>
+          <t>Security Flaw Assessment</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -33014,7 +33070,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>vulnerability assessment; penetration testing; network scanning; threat modeling; modern tools</t>
+          <t>vulnerability assessment; penetration testing; network scanning; threat modeling; security flaw</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
@@ -33029,19 +33085,15 @@
         </is>
       </c>
       <c r="R251" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S251" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T251" t="inlineStr"/>
       <c r="U251" t="inlineStr">
         <is>
-          <t>keep:0, "Vulnerability Assessment":3</t>
+          <t>keep:2, "Vulnerability Assessment":1</t>
         </is>
       </c>
       <c r="V251" t="inlineStr">
@@ -33061,13 +33113,9 @@
         <v>1</v>
       </c>
       <c r="Z251" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA251" t="inlineStr">
-        <is>
-          <t>System Vulnerability Analysis</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA251" t="inlineStr"/>
       <c r="AB251" t="b">
         <v>0</v>
       </c>
@@ -33166,12 +33214,12 @@
         <v>0</v>
       </c>
       <c r="S252" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="T252" t="inlineStr"/>
       <c r="U252" t="inlineStr">
         <is>
-          <t>keep:0, "Security Paradigm Evaluation":1, "Security Paradigm Analysis":1, "Security Paradigm Review":1</t>
+          <t>keep:2, "Security Paradigm Analysis":1</t>
         </is>
       </c>
       <c r="V252" t="inlineStr">
@@ -33301,7 +33349,7 @@
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>keep:1, "Security Protocol Application":2</t>
+          <t>keep:0, "Security Protocol Application":2, "Security Protocol Implementation":1</t>
         </is>
       </c>
       <c r="V253" t="inlineStr">
@@ -33373,7 +33421,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>System Vulnerability Analysis</t>
+          <t>Vulnerability Analysis</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -33404,7 +33452,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>cybersecurity; threat modelling; network scanning; vulnerability assessment; security flaws</t>
+          <t>cybersecurity; penetration testing; threat modeling; network scanning; vulnerability assessment</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
@@ -33419,19 +33467,15 @@
         </is>
       </c>
       <c r="R254" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S254" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T254" t="inlineStr"/>
       <c r="U254" t="inlineStr">
         <is>
-          <t>keep:0, "System Vulnerability Analysis/Vulnerability Analysis":3</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V254" t="inlineStr">
@@ -33448,12 +33492,16 @@
         </is>
       </c>
       <c r="Y254" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z254" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA254" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>Security Flaw Assessment</t>
+        </is>
+      </c>
       <c r="AB254" t="b">
         <v>0</v>
       </c>
@@ -33508,7 +33556,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Examines web security assessments incorporating system, network, and cloud analyses in hybrid environments.</t>
+          <t>Provides comprehensive web security assessments integrating system, network, and cloud considerations in hybrid environments.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -33552,12 +33600,12 @@
         <v>0</v>
       </c>
       <c r="S255" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T255" t="inlineStr"/>
       <c r="U255" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Web Security Analysis":1</t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
@@ -33629,12 +33677,12 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Business Model Development</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Develops ideas into viable businesses by systematically following hybrid development steps to create comprehensive models.</t>
+          <t>Develops ideas into viable businesses by systematically developing hybrid development steps to develop comprehensive models.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -33660,7 +33708,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>business model canvas; value proposition; revenue streams; market analysis; business development</t>
+          <t>business model canvas; value proposition; revenue streams; market analysis; lean startup</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
@@ -33675,19 +33723,15 @@
         </is>
       </c>
       <c r="R256" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S256" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T256" t="inlineStr"/>
       <c r="U256" t="inlineStr">
         <is>
-          <t>keep:1, "Business Development":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V256" t="inlineStr">
@@ -33704,7 +33748,7 @@
         </is>
       </c>
       <c r="Y256" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z256" t="b">
         <v>0</v>
@@ -33790,7 +33834,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>theoretical application; qualitative analysis; business frameworks; critical thinking; case studies</t>
+          <t>theoretical application; business frameworks; critical thinking; case study; qualitative analysis</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
@@ -33805,19 +33849,15 @@
         </is>
       </c>
       <c r="R257" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S257" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="T257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T257" t="inlineStr"/>
       <c r="U257" t="inlineStr">
         <is>
-          <t>keep:0, "Case Study Analysis":2, "Case Study Application":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
@@ -33889,12 +33929,12 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Debate Facilitation</t>
+          <t>Debate Analysis</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Applies ethical theory to analyse dilemmas in hybrid in‑person and virtual debates, structuring arguments, moderating dialogue, and ensuring balanced participation.</t>
+          <t>Applies ethical theory to analyse ethical dilemmas in IT and business through hybrid in‑person and virtual debates, structuring arguments, moderating dialogue, and ensuring balanced participation.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -33920,7 +33960,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>debate; facilitation; public speaking; argumentation; critical thinking</t>
+          <t>moderation; public speaking; argumentation; critical thinking; debate</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
@@ -33947,7 +33987,7 @@
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>keep:0, "Debate Facilitation":2, "Debate Analysis":1</t>
+          <t>keep:0, "Debate Analysis/Ethical Debate Analysis":2, "Debate Application":1</t>
         </is>
       </c>
       <c r="V258" t="inlineStr">
@@ -34024,7 +34064,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Evaluates multiple funding sources and supports venture development stages in hybrid settings.</t>
+          <t>Evaluates multiple funding sources to support venture development stages in hybrid settings.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -34050,7 +34090,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>venture financing; funding sources analysis; startup development stages; funding options; market opportunity assessment</t>
+          <t>venture financing; funding sources analysis; funding options; business model validation; market opportunity assessment</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
@@ -34101,7 +34141,7 @@
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>Funding Options Evaluation</t>
+          <t>Funding Options Analysis</t>
         </is>
       </c>
       <c r="AB259" t="b">
@@ -34184,7 +34224,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>ethical theory; IT ethics; business ethics; moral reasoning; ethical dilemma</t>
+          <t>ethical theory; IT ethics; business ethics; moral reasoning; ethical dilemmas</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
@@ -34206,12 +34246,12 @@
       </c>
       <c r="T260" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>keep:1, "Ethical Dilemma Analysis":2</t>
+          <t>keep:0, "Ethical Dilemma Analysis":3</t>
         </is>
       </c>
       <c r="V260" t="inlineStr">
@@ -34288,7 +34328,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Applies ethical theories to analyse IT and business dilemmas for responsible decision-making.</t>
+          <t>Applies ethical theories to analyse IT and business dilemmas.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -34314,7 +34354,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>business ethics; IT governance; moral philosophy; ethical decision‑making models; ethical theory</t>
+          <t>business ethics; moral philosophy; ethical decision‑making models; stakeholder analysis; ethical theory application</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
@@ -34332,12 +34372,12 @@
         <v>0</v>
       </c>
       <c r="S261" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T261" t="inlineStr"/>
       <c r="U261" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Ethical Theory Application":1</t>
         </is>
       </c>
       <c r="V261" t="inlineStr">
@@ -34409,7 +34449,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Funding Options Evaluation</t>
+          <t>Funding Options Analysis</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -34440,7 +34480,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>venture financing; grant sourcing; alternative financing mechanisms; funding options; capital structure analysis</t>
+          <t>venture financing; grant sourcing; funding options; alternative financing mechanisms; financial modeling</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
@@ -34455,19 +34495,15 @@
         </is>
       </c>
       <c r="R262" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S262" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T262" t="inlineStr"/>
       <c r="U262" t="inlineStr">
         <is>
-          <t>keep:1, "Funding Options Evaluation":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V262" t="inlineStr">
@@ -34539,7 +34575,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Entrepreneurship Principles Development</t>
+          <t>Entrepreneurship Principles Instruction</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -34570,7 +34606,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>venture creation; business model development; lean startup methodology; entrepreneurship; principles</t>
+          <t>venture creation; business model development; lean startup methodology; entrepreneurship principles; instruction</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
@@ -34597,7 +34633,7 @@
       </c>
       <c r="U263" t="inlineStr">
         <is>
-          <t>keep:0, "Entrepreneurship Principle Development/Entrepreneurship Principles Development":3</t>
+          <t>keep:0, "Entrepreneurship Principles Instruction":3</t>
         </is>
       </c>
       <c r="V263" t="inlineStr">
@@ -34669,12 +34705,12 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Legal Compliance Evaluation</t>
+          <t>Legal Social Ethical Analysis</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Analyses IT ventures to assess social, legal, ethical implications and ensure compliance.</t>
+          <t>Analyses IT ventures to identify social, legal and ethical implications and ensure compliance.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -34700,7 +34736,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>regulatory compliance; legal compliance; risk assessment; ethical analysis; data protection</t>
+          <t>regulatory compliance; ethical analysis; data protection; legal compliance; social implications</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
@@ -34715,15 +34751,19 @@
         </is>
       </c>
       <c r="R264" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S264" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T264" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>keep:1, "Social-Legal-Ethical Compliance Evaluation":1, "Legal Social Ethical Analysis":1</t>
+          <t>keep:1, "Legal Social Ethical Analysis":2</t>
         </is>
       </c>
       <c r="V264" t="inlineStr">
@@ -34743,9 +34783,13 @@
         <v>1</v>
       </c>
       <c r="Z264" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA264" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>Social-legal-ethical Impact Assessment</t>
+        </is>
+      </c>
       <c r="AB264" t="b">
         <v>0</v>
       </c>
@@ -34849,7 +34893,7 @@
       <c r="T265" t="inlineStr"/>
       <c r="U265" t="inlineStr">
         <is>
-          <t>keep:2, "Personal Viewpoint Reflection Development":1</t>
+          <t>keep:2, "Personal Reflection Development":1</t>
         </is>
       </c>
       <c r="V265" t="inlineStr">
@@ -34974,12 +35018,12 @@
       </c>
       <c r="T266" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>keep:0, "Reflection Presentation Development":3</t>
+          <t>keep:0, "Reflection Presentation Development":2, "Personal Reflection Presentation":1</t>
         </is>
       </c>
       <c r="V266" t="inlineStr">
@@ -35056,7 +35100,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Evaluates IT ventures in hybrid settings, assessing social, legal, ethical impacts for decisions.</t>
+          <t>Analyses IT ventures in hybrid settings to determine social, legal and ethical impacts.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -35104,12 +35148,12 @@
       </c>
       <c r="T267" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U267" t="inlineStr">
         <is>
-          <t>keep:0, "Social-Legal-Ethical Impact Assessment":2, "Social Legal Ethical Assessment":1</t>
+          <t>keep:0, "Social-Legal-Ethical Impact Assessment/Social-Legal-Ethical Assessment":3</t>
         </is>
       </c>
       <c r="V267" t="inlineStr">
@@ -35129,13 +35173,9 @@
         <v>1</v>
       </c>
       <c r="Z267" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA267" t="inlineStr">
-        <is>
-          <t>Legal Compliance Evaluation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA267" t="inlineStr"/>
       <c r="AB267" t="b">
         <v>0</v>
       </c>
@@ -35185,12 +35225,12 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Stakeholder Responsibility Assessment</t>
+          <t>IT Professional Responsibility Assessment</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Analyses and examines IT professional duties to employers, clients, and society within team discussions.</t>
+          <t>Analyses IT professional duties to employers, clients, and society within team discussions.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -35216,7 +35256,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>professional ethics; corporate social responsibility; stakeholder analysis; accountability; employer responsibilities</t>
+          <t>professional ethics; corporate social responsibility; stakeholder analysis; accountability; legal issues</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
@@ -35234,16 +35274,16 @@
         <v>1</v>
       </c>
       <c r="S268" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U268" t="inlineStr">
         <is>
-          <t>keep:0, "Stakeholder Responsibility Assessment":3</t>
+          <t>keep:1, "IT Professional Responsibility Assessment":2</t>
         </is>
       </c>
       <c r="V268" t="inlineStr">
@@ -35315,7 +35355,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Startup Issue Identification</t>
+          <t>Startup Risk Identification</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -35346,7 +35386,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>entrepreneurship; risk assessment; lean startup methodology; market feasibility; startup issues</t>
+          <t>entrepreneurship; risk assessment; venture validation; lean startup methodology; market feasibility</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
@@ -35361,19 +35401,15 @@
         </is>
       </c>
       <c r="R269" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S269" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T269" t="inlineStr"/>
       <c r="U269" t="inlineStr">
         <is>
-          <t>keep:1, "Startup Issue Identification":2</t>
+          <t>keep:1, "Startup Issues Discussion":1, "Startup Pitfall Identification":1</t>
         </is>
       </c>
       <c r="V269" t="inlineStr">
@@ -35390,7 +35426,7 @@
         </is>
       </c>
       <c r="Y269" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z269" t="b">
         <v>0</v>
@@ -35445,12 +35481,12 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Team Collaboration Management</t>
+          <t>Team Collaboration</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Analyses hybrid team efforts and examines tasks and communication to achieve shared objectives.</t>
+          <t>Analyses team responsibilities and examines ethical issues in IT business ventures as part of a collaborative effort.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -35491,15 +35527,19 @@
         </is>
       </c>
       <c r="R270" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S270" t="n">
-        <v>0</v>
-      </c>
-      <c r="T270" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>keep:0, "Team Collaboration Coordination":1, "Team Collaboration":1, "Team Participation":1</t>
+          <t>keep:0, "Team Collaboration":3</t>
         </is>
       </c>
       <c r="V270" t="inlineStr">
@@ -35571,7 +35611,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Activity Tracking Reporting</t>
+          <t>Activity Reporting</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -35602,7 +35642,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>project scheduling; activity tracking; performance metrics; Gantt chart; dashboard reporting</t>
+          <t>project scheduling; stakeholder communication; performance metrics; activity tracking; dashboard reporting</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
@@ -35624,12 +35664,12 @@
       </c>
       <c r="T271" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U271" t="inlineStr">
         <is>
-          <t>keep:0, "Activity Tracking Reporting/Activity Reporting/Project Activity Reporting":3</t>
+          <t>keep:0, "Activity Reporting/Activity Tracking Reporting":2, "Activity Tracking":1</t>
         </is>
       </c>
       <c r="V271" t="inlineStr">
@@ -35705,7 +35745,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Cost Management Analysis</t>
+          <t>Cost Management</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -35751,15 +35791,19 @@
         </is>
       </c>
       <c r="R272" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S272" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T272" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>keep:2, "Cost Management Analysis":1</t>
+          <t>keep:1, "Cost Management":2</t>
         </is>
       </c>
       <c r="V272" t="inlineStr">
@@ -35783,7 +35827,7 @@
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>Resource Allocation Planning</t>
+          <t>Project Planning</t>
         </is>
       </c>
       <c r="AB272" t="b">
@@ -35835,7 +35879,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Project Documentation Development</t>
+          <t>Project Design Documentation Development</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -35866,7 +35910,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>technical writing; project planning; documentation standards; realistic plans; Confluence</t>
+          <t>technical writing; project planning; documentation standards; deliverables; design documentation</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
@@ -35884,7 +35928,7 @@
         <v>1</v>
       </c>
       <c r="S273" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -35974,7 +36018,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Refers to integrated project schedules, timelines, costs, and resources to drive on‑time delivery.</t>
+          <t>Refers to integrated project schedules that incorporate timelines, costs, and resources to support on‑time delivery.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -36000,7 +36044,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>scheduling; cost control; resource allocation; resource management; MS Project</t>
+          <t>scheduling; cost control; resource allocation; critical path method; MS Project</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -36044,14 +36088,14 @@
         </is>
       </c>
       <c r="Y274" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z274" t="b">
         <v>1</v>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>Cost Management Analysis</t>
+          <t>Resource Allocation Planning</t>
         </is>
       </c>
       <c r="AB274" t="b">
@@ -36108,7 +36152,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Plans detailed, achievable project plans, ensuring timelines, resources, and constraints meet realistic goals.</t>
+          <t>Prepares detailed, achievable project plans with timelines, resources, and constraints set to realistic goals.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -36157,7 +36201,7 @@
       <c r="T275" t="inlineStr"/>
       <c r="U275" t="inlineStr">
         <is>
-          <t>keep:2, "Project Planning":1</t>
+          <t>keep:2, "Realistic Project Planning":1</t>
         </is>
       </c>
       <c r="V275" t="inlineStr">
@@ -36229,7 +36273,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Requirements Refinement Documentation</t>
+          <t>System Requirements Documentation</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -36260,7 +36304,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>requirements analysis; system specification; traceability matrix; business analysis; requirements refinement</t>
+          <t>requirements analysis; system specification; traceability matrix; business analysis; system requirements</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
@@ -36278,7 +36322,7 @@
         <v>1</v>
       </c>
       <c r="S276" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -36287,7 +36331,7 @@
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>keep:0, "Requirements Refinement Documentation/System Requirements Refinement Documentation":3</t>
+          <t>keep:0, "System Requirements Documentation/Requirements Documentation":3</t>
         </is>
       </c>
       <c r="V276" t="inlineStr">
@@ -36307,9 +36351,13 @@
         <v>1</v>
       </c>
       <c r="Z276" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA276" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>System Requirements Development</t>
+        </is>
+      </c>
       <c r="AB276" t="b">
         <v>0</v>
       </c>
@@ -36413,7 +36461,7 @@
       <c r="T277" t="inlineStr"/>
       <c r="U277" t="inlineStr">
         <is>
-          <t>keep:1, "Project Schedule Planning":1, "Resource Allocation Planning":1</t>
+          <t>keep:2, "Resource Management Planning":1</t>
         </is>
       </c>
       <c r="V277" t="inlineStr">
@@ -36538,12 +36586,12 @@
       </c>
       <c r="T278" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U278" t="inlineStr">
         <is>
-          <t>keep:0, "Risk Management":3</t>
+          <t>keep:0, "Risk Management":2, "Risk Mitigation":1</t>
         </is>
       </c>
       <c r="V278" t="inlineStr">
@@ -36646,7 +36694,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>cybersecurity risk assessment; project lifecycle security; risk mitigation strategies; security architecture integration; security analysis</t>
+          <t>cybersecurity risk assessment; project lifecycle security; risk mitigation strategies; security architecture integration; project management framework</t>
         </is>
       </c>
       <c r="O279" t="inlineStr">
@@ -36750,7 +36798,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Reports concise status updates on project schedules and activity data to stakeholders.</t>
+          <t>Reports concise status updates to stakeholders.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -36875,7 +36923,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>System Requirements Analysis</t>
+          <t>System Requirements Development</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -36924,7 +36972,7 @@
         <v>1</v>
       </c>
       <c r="S281" t="n">
-        <v>0.925</v>
+        <v>0.9</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -36933,7 +36981,7 @@
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>keep:0, "System Requirements Analysis":2, "System Requirements Development":1</t>
+          <t>keep:0, "System Requirements Development":2, "System Requirements Analysis":1</t>
         </is>
       </c>
       <c r="V281" t="inlineStr">
@@ -37005,7 +37053,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Team Meeting Facilitation</t>
+          <t>Team Meeting Preparation</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -37036,7 +37084,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>collaborative meetings; team dynamics; agenda planning; stakeholder engagement; meeting facilitation tools</t>
+          <t>collaborative meetings; team dynamics; agenda planning; stakeholder engagement; project team meetings</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
@@ -37054,16 +37102,16 @@
         <v>1</v>
       </c>
       <c r="S282" t="n">
-        <v>0.925</v>
+        <v>0.9</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U282" t="inlineStr">
         <is>
-          <t>keep:1, "Team Meeting Facilitation":2</t>
+          <t>keep:0, "Project Team Meeting Preparation/Team Meeting Preparation":3</t>
         </is>
       </c>
       <c r="V282" t="inlineStr">
@@ -37080,7 +37128,7 @@
         </is>
       </c>
       <c r="Y282" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z282" t="b">
         <v>0</v>
@@ -37135,12 +37183,12 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Design Documentation</t>
+          <t>Design Documentation Compliance</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Develops professional project design documentation that satisfies software and cybersecurity industry standards.</t>
+          <t>Designs professional project documentation that satisfies software and cybersecurity industry standards.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -37158,7 +37206,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>theoretical</t>
+          <t>practical</t>
         </is>
       </c>
       <c r="M283" t="n">
@@ -37166,7 +37214,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>project design documentation; design documentation; industry standards; software requirements; cybersecurity compliance</t>
+          <t>project design; industry standards; documentation compliance; professional documentation; cybersecurity industry standards</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
@@ -37177,7 +37225,7 @@
       <c r="P283" t="inlineStr"/>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>Design Documentation</t>
+          <t>Design Documentation Compliance</t>
         </is>
       </c>
       <c r="R283" t="b">
@@ -37202,7 +37250,7 @@
       </c>
       <c r="X283" t="inlineStr">
         <is>
-          <t>design documentation, industry standards, software requirements, cybersecurity compliance, professional documentation</t>
+          <t>project design, industry standards, documentation compliance, software security, professional documentation</t>
         </is>
       </c>
       <c r="Y283" t="b">
